--- a/output/yearly_population_iteration_40_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_40_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6011</v>
+        <v>5499</v>
       </c>
       <c r="C2" t="n">
-        <v>12370</v>
+        <v>7586</v>
       </c>
       <c r="D2" t="n">
-        <v>36313</v>
+        <v>17976</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4210</v>
+        <v>3731</v>
       </c>
       <c r="C3" t="n">
-        <v>4941</v>
+        <v>5857</v>
       </c>
       <c r="D3" t="n">
-        <v>15756</v>
+        <v>13430</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3175</v>
+        <v>2982</v>
       </c>
       <c r="C4" t="n">
-        <v>4215</v>
+        <v>5160</v>
       </c>
       <c r="D4" t="n">
-        <v>6820</v>
+        <v>6825</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2022</v>
+        <v>1889</v>
       </c>
       <c r="C5" t="n">
-        <v>3429</v>
+        <v>4007</v>
       </c>
       <c r="D5" t="n">
-        <v>2490</v>
+        <v>2721</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1203</v>
+        <v>1019</v>
       </c>
       <c r="C6" t="n">
-        <v>2283</v>
+        <v>2794</v>
       </c>
       <c r="D6" t="n">
-        <v>1108</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>605</v>
+        <v>445</v>
       </c>
       <c r="C7" t="n">
-        <v>1461</v>
+        <v>1906</v>
       </c>
       <c r="D7" t="n">
-        <v>638</v>
+        <v>661</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>225</v>
+        <v>168</v>
       </c>
       <c r="C8" t="n">
-        <v>811</v>
+        <v>986</v>
       </c>
       <c r="D8" t="n">
-        <v>436</v>
+        <v>432</v>
       </c>
     </row>
     <row r="9">
@@ -878,10 +878,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="C9" t="n">
-        <v>383</v>
+        <v>415</v>
       </c>
       <c r="D9" t="n">
         <v>307</v>
@@ -895,10 +895,10 @@
         <v>39</v>
       </c>
       <c r="C10" t="n">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="D10" t="n">
-        <v>246</v>
+        <v>243</v>
       </c>
     </row>
     <row r="11">
@@ -909,7 +909,7 @@
         <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="D11" t="n">
         <v>206</v>
@@ -926,7 +926,7 @@
         <v>129</v>
       </c>
       <c r="D12" t="n">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D13" t="n">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="14">
@@ -948,10 +948,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D14" t="n">
         <v>101</v>
@@ -965,7 +965,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
         <v>79</v>
@@ -979,7 +979,7 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D16" t="n">
         <v>65</v>
@@ -993,10 +993,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1007,7 +1007,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
         <v>39</v>
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1049,10 +1049,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7374</v>
+        <v>8912</v>
       </c>
       <c r="C2" t="n">
-        <v>12387</v>
+        <v>5001</v>
       </c>
       <c r="D2" t="n">
-        <v>29876</v>
+        <v>23680</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4100</v>
+        <v>3691</v>
       </c>
       <c r="C3" t="n">
-        <v>7371</v>
+        <v>5845</v>
       </c>
       <c r="D3" t="n">
-        <v>17492</v>
+        <v>13145</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3102</v>
+        <v>2834</v>
       </c>
       <c r="C4" t="n">
-        <v>4482</v>
+        <v>5337</v>
       </c>
       <c r="D4" t="n">
-        <v>8005</v>
+        <v>7629</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2230</v>
+        <v>2106</v>
       </c>
       <c r="C5" t="n">
-        <v>3694</v>
+        <v>4466</v>
       </c>
       <c r="D5" t="n">
-        <v>3120</v>
+        <v>3308</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1436</v>
+        <v>1264</v>
       </c>
       <c r="C6" t="n">
-        <v>2788</v>
+        <v>3286</v>
       </c>
       <c r="D6" t="n">
-        <v>1294</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>774</v>
+        <v>616</v>
       </c>
       <c r="C7" t="n">
-        <v>1816</v>
+        <v>2305</v>
       </c>
       <c r="D7" t="n">
-        <v>705</v>
+        <v>732</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>339</v>
+        <v>253</v>
       </c>
       <c r="C8" t="n">
-        <v>1097</v>
+        <v>1372</v>
       </c>
       <c r="D8" t="n">
-        <v>456</v>
+        <v>461</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>123</v>
+        <v>93</v>
       </c>
       <c r="C9" t="n">
-        <v>559</v>
+        <v>655</v>
       </c>
       <c r="D9" t="n">
-        <v>322</v>
+        <v>318</v>
       </c>
     </row>
     <row r="10">
@@ -1203,10 +1203,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C10" t="n">
-        <v>286</v>
+        <v>296</v>
       </c>
       <c r="D10" t="n">
         <v>249</v>
@@ -1223,7 +1223,7 @@
         <v>186</v>
       </c>
       <c r="D11" t="n">
-        <v>209</v>
+        <v>206</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D12" t="n">
-        <v>160</v>
+        <v>164</v>
       </c>
     </row>
     <row r="13">
@@ -1248,10 +1248,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D13" t="n">
-        <v>128</v>
+        <v>125</v>
       </c>
     </row>
     <row r="14">
@@ -1259,10 +1259,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D14" t="n">
         <v>102</v>
@@ -1276,7 +1276,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D15" t="n">
         <v>79</v>
@@ -1290,7 +1290,7 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D16" t="n">
         <v>65</v>
@@ -1304,10 +1304,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1318,7 +1318,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
         <v>39</v>
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1360,10 +1360,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9448</v>
+        <v>9352</v>
       </c>
       <c r="C2" t="n">
-        <v>7445</v>
+        <v>4807</v>
       </c>
       <c r="D2" t="n">
-        <v>36166</v>
+        <v>22960</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4431</v>
+        <v>4658</v>
       </c>
       <c r="C3" t="n">
-        <v>8407</v>
+        <v>4870</v>
       </c>
       <c r="D3" t="n">
-        <v>17929</v>
+        <v>13631</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3000</v>
+        <v>2716</v>
       </c>
       <c r="C4" t="n">
-        <v>5692</v>
+        <v>5399</v>
       </c>
       <c r="D4" t="n">
-        <v>9218</v>
+        <v>8244</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2323</v>
+        <v>2138</v>
       </c>
       <c r="C5" t="n">
-        <v>3922</v>
+        <v>4749</v>
       </c>
       <c r="D5" t="n">
-        <v>3698</v>
+        <v>3797</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1604</v>
+        <v>1459</v>
       </c>
       <c r="C6" t="n">
-        <v>3145</v>
+        <v>3711</v>
       </c>
       <c r="D6" t="n">
-        <v>1539</v>
+        <v>1634</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>936</v>
+        <v>790</v>
       </c>
       <c r="C7" t="n">
-        <v>2197</v>
+        <v>2707</v>
       </c>
       <c r="D7" t="n">
-        <v>771</v>
+        <v>805</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>453</v>
+        <v>346</v>
       </c>
       <c r="C8" t="n">
-        <v>1374</v>
+        <v>1723</v>
       </c>
       <c r="D8" t="n">
-        <v>485</v>
+        <v>493</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>181</v>
+        <v>134</v>
       </c>
       <c r="C9" t="n">
-        <v>769</v>
+        <v>922</v>
       </c>
       <c r="D9" t="n">
-        <v>332</v>
+        <v>329</v>
       </c>
     </row>
     <row r="10">
@@ -1514,10 +1514,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C10" t="n">
-        <v>384</v>
+        <v>429</v>
       </c>
       <c r="D10" t="n">
         <v>255</v>
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C11" t="n">
         <v>222</v>
       </c>
       <c r="D11" t="n">
-        <v>209</v>
+        <v>206</v>
       </c>
     </row>
     <row r="12">
@@ -1545,10 +1545,10 @@
         <v>19</v>
       </c>
       <c r="C12" t="n">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D12" t="n">
-        <v>164</v>
+        <v>167</v>
       </c>
     </row>
     <row r="13">
@@ -1559,10 +1559,10 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D13" t="n">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="14">
@@ -1570,10 +1570,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D14" t="n">
         <v>103</v>
@@ -1587,7 +1587,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D15" t="n">
         <v>79</v>
@@ -1601,7 +1601,7 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D16" t="n">
         <v>65</v>
@@ -1615,10 +1615,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1629,7 +1629,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
         <v>39</v>
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1671,10 +1671,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="D21" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8514</v>
+        <v>8483</v>
       </c>
       <c r="C2" t="n">
-        <v>5003</v>
+        <v>3230</v>
       </c>
       <c r="D2" t="n">
-        <v>29621</v>
+        <v>18891</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5387</v>
+        <v>5290</v>
       </c>
       <c r="C3" t="n">
-        <v>11318</v>
+        <v>7467</v>
       </c>
       <c r="D3" t="n">
-        <v>19266</v>
+        <v>15015</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2146</v>
+        <v>1975</v>
       </c>
       <c r="C4" t="n">
-        <v>6934</v>
+        <v>7565</v>
       </c>
       <c r="D4" t="n">
-        <v>8626</v>
+        <v>8048</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1482</v>
+        <v>1348</v>
       </c>
       <c r="C5" t="n">
-        <v>3082</v>
+        <v>3636</v>
       </c>
       <c r="D5" t="n">
-        <v>2537</v>
+        <v>2658</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>864</v>
+        <v>729</v>
       </c>
       <c r="C6" t="n">
-        <v>2153</v>
+        <v>2652</v>
       </c>
       <c r="D6" t="n">
-        <v>755</v>
+        <v>788</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>418</v>
+        <v>319</v>
       </c>
       <c r="C7" t="n">
-        <v>1346</v>
+        <v>1688</v>
       </c>
       <c r="D7" t="n">
-        <v>475</v>
+        <v>483</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>167</v>
+        <v>123</v>
       </c>
       <c r="C8" t="n">
-        <v>753</v>
+        <v>903</v>
       </c>
       <c r="D8" t="n">
-        <v>325</v>
+        <v>322</v>
       </c>
     </row>
     <row r="9">
@@ -1811,10 +1811,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="C9" t="n">
-        <v>376</v>
+        <v>420</v>
       </c>
       <c r="D9" t="n">
         <v>249</v>
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C10" t="n">
         <v>217</v>
       </c>
       <c r="D10" t="n">
-        <v>204</v>
+        <v>201</v>
       </c>
     </row>
     <row r="11">
@@ -1842,10 +1842,10 @@
         <v>17</v>
       </c>
       <c r="C11" t="n">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D11" t="n">
-        <v>160</v>
+        <v>163</v>
       </c>
     </row>
     <row r="12">
@@ -1856,10 +1856,10 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D12" t="n">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="13">
@@ -1867,10 +1867,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C13" t="n">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="D13" t="n">
         <v>100</v>
@@ -1884,7 +1884,7 @@
         <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D14" t="n">
         <v>77</v>
@@ -1898,7 +1898,7 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D15" t="n">
         <v>63</v>
@@ -1912,10 +1912,10 @@
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D16" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="17">
@@ -1926,7 +1926,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D17" t="n">
         <v>38</v>
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D19" t="n">
         <v>15</v>
@@ -1968,10 +1968,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="D20" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5166</v>
+        <v>4882</v>
       </c>
       <c r="C2" t="n">
-        <v>2416</v>
+        <v>2258</v>
       </c>
       <c r="D2" t="n">
-        <v>20764</v>
+        <v>13603</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5775</v>
+        <v>5712</v>
       </c>
       <c r="C3" t="n">
-        <v>7622</v>
+        <v>4999</v>
       </c>
       <c r="D3" t="n">
-        <v>19564</v>
+        <v>14677</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2959</v>
+        <v>2822</v>
       </c>
       <c r="C4" t="n">
-        <v>9118</v>
+        <v>7579</v>
       </c>
       <c r="D4" t="n">
-        <v>10163</v>
+        <v>9027</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1653</v>
+        <v>1508</v>
       </c>
       <c r="C5" t="n">
-        <v>4726</v>
+        <v>5394</v>
       </c>
       <c r="D5" t="n">
-        <v>3268</v>
+        <v>3300</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1032</v>
+        <v>880</v>
       </c>
       <c r="C6" t="n">
-        <v>2613</v>
+        <v>3162</v>
       </c>
       <c r="D6" t="n">
-        <v>939</v>
+        <v>981</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>394</v>
+        <v>299</v>
       </c>
       <c r="C7" t="n">
-        <v>1685</v>
+        <v>2084</v>
       </c>
       <c r="D7" t="n">
-        <v>517</v>
+        <v>527</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>137</v>
+        <v>104</v>
       </c>
       <c r="C8" t="n">
-        <v>958</v>
+        <v>1176</v>
       </c>
       <c r="D8" t="n">
-        <v>339</v>
+        <v>336</v>
       </c>
     </row>
     <row r="9">
@@ -2122,10 +2122,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C9" t="n">
-        <v>431</v>
+        <v>477</v>
       </c>
       <c r="D9" t="n">
         <v>258</v>
@@ -2139,10 +2139,10 @@
         <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D10" t="n">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="11">
@@ -2153,10 +2153,10 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D11" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D12" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="13">
@@ -2181,7 +2181,7 @@
         <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D13" t="n">
         <v>97</v>
@@ -2195,7 +2195,7 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D14" t="n">
         <v>61</v>
@@ -2209,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -2223,7 +2223,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D16" t="n">
         <v>37</v>
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D18" t="n">
         <v>14</v>
@@ -2265,10 +2265,10 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5363</v>
+        <v>5945</v>
       </c>
       <c r="C2" t="n">
-        <v>8091</v>
+        <v>8077</v>
       </c>
       <c r="D2" t="n">
-        <v>20969</v>
+        <v>13407</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4630</v>
+        <v>4502</v>
       </c>
       <c r="C3" t="n">
-        <v>4517</v>
+        <v>3260</v>
       </c>
       <c r="D3" t="n">
-        <v>18578</v>
+        <v>13512</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3604</v>
+        <v>3486</v>
       </c>
       <c r="C4" t="n">
-        <v>8181</v>
+        <v>6133</v>
       </c>
       <c r="D4" t="n">
-        <v>11290</v>
+        <v>9728</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1960</v>
+        <v>1839</v>
       </c>
       <c r="C5" t="n">
-        <v>6781</v>
+        <v>6330</v>
       </c>
       <c r="D5" t="n">
-        <v>4293</v>
+        <v>4134</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1188</v>
+        <v>1060</v>
       </c>
       <c r="C6" t="n">
-        <v>3540</v>
+        <v>4189</v>
       </c>
       <c r="D6" t="n">
-        <v>1284</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>573</v>
+        <v>464</v>
       </c>
       <c r="C7" t="n">
-        <v>2110</v>
+        <v>2578</v>
       </c>
       <c r="D7" t="n">
-        <v>578</v>
+        <v>588</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>200</v>
+        <v>152</v>
       </c>
       <c r="C8" t="n">
-        <v>1266</v>
+        <v>1560</v>
       </c>
       <c r="D8" t="n">
-        <v>358</v>
+        <v>362</v>
       </c>
     </row>
     <row r="9">
@@ -2433,10 +2433,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="C9" t="n">
-        <v>636</v>
+        <v>748</v>
       </c>
       <c r="D9" t="n">
         <v>264</v>
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C10" t="n">
-        <v>307</v>
+        <v>322</v>
       </c>
       <c r="D10" t="n">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="11">
@@ -2464,10 +2464,10 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D11" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D12" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D14" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="15">
@@ -2520,7 +2520,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D15" t="n">
         <v>48</v>
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D16" t="n">
         <v>36</v>
@@ -2562,7 +2562,7 @@
         <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D18" t="n">
         <v>13</v>
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3205</v>
+        <v>3465</v>
       </c>
       <c r="C2" t="n">
-        <v>3725</v>
+        <v>3697</v>
       </c>
       <c r="D2" t="n">
-        <v>14451</v>
+        <v>9242</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4636</v>
+        <v>4687</v>
       </c>
       <c r="C3" t="n">
-        <v>5601</v>
+        <v>4812</v>
       </c>
       <c r="D3" t="n">
-        <v>18399</v>
+        <v>13175</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3985</v>
+        <v>3868</v>
       </c>
       <c r="C4" t="n">
-        <v>7643</v>
+        <v>5628</v>
       </c>
       <c r="D4" t="n">
-        <v>12337</v>
+        <v>10262</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2063</v>
+        <v>1915</v>
       </c>
       <c r="C5" t="n">
-        <v>8020</v>
+        <v>7169</v>
       </c>
       <c r="D5" t="n">
-        <v>4543</v>
+        <v>4484</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1012</v>
+        <v>869</v>
       </c>
       <c r="C6" t="n">
-        <v>4348</v>
+        <v>5149</v>
       </c>
       <c r="D6" t="n">
-        <v>1261</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>184</v>
+        <v>140</v>
       </c>
       <c r="C7" t="n">
-        <v>2249</v>
+        <v>2782</v>
       </c>
       <c r="D7" t="n">
-        <v>579</v>
+        <v>590</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="C8" t="n">
-        <v>1020</v>
+        <v>1222</v>
       </c>
       <c r="D8" t="n">
-        <v>377</v>
+        <v>383</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>300</v>
+        <v>315</v>
       </c>
       <c r="D9" t="n">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="10">
@@ -2761,10 +2761,10 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D10" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D11" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14">
@@ -2817,7 +2817,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D14" t="n">
         <v>47</v>
@@ -2831,7 +2831,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D15" t="n">
         <v>35</v>
@@ -2859,7 +2859,7 @@
         <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
         <v>12</v>
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3975</v>
+        <v>3733</v>
       </c>
       <c r="C2" t="n">
-        <v>5833</v>
+        <v>4342</v>
       </c>
       <c r="D2" t="n">
-        <v>12749</v>
+        <v>15915</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3421</v>
+        <v>3560</v>
       </c>
       <c r="C3" t="n">
-        <v>4208</v>
+        <v>3771</v>
       </c>
       <c r="D3" t="n">
-        <v>16625</v>
+        <v>11754</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3752</v>
+        <v>3673</v>
       </c>
       <c r="C4" t="n">
-        <v>6577</v>
+        <v>5165</v>
       </c>
       <c r="D4" t="n">
-        <v>12951</v>
+        <v>10425</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2518</v>
+        <v>2404</v>
       </c>
       <c r="C5" t="n">
-        <v>7760</v>
+        <v>6378</v>
       </c>
       <c r="D5" t="n">
-        <v>5645</v>
+        <v>5235</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1292</v>
+        <v>1162</v>
       </c>
       <c r="C6" t="n">
-        <v>5901</v>
+        <v>6023</v>
       </c>
       <c r="D6" t="n">
-        <v>1685</v>
+        <v>1748</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>385</v>
+        <v>325</v>
       </c>
       <c r="C7" t="n">
-        <v>3135</v>
+        <v>3809</v>
       </c>
       <c r="D7" t="n">
-        <v>665</v>
+        <v>673</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>84</v>
+        <v>67</v>
       </c>
       <c r="C8" t="n">
-        <v>1485</v>
+        <v>1826</v>
       </c>
       <c r="D8" t="n">
-        <v>398</v>
+        <v>407</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C9" t="n">
-        <v>541</v>
+        <v>626</v>
       </c>
       <c r="D9" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="10">
@@ -3072,10 +3072,10 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="D10" t="n">
-        <v>173</v>
+        <v>177</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D11" t="n">
-        <v>137</v>
+        <v>134</v>
       </c>
     </row>
     <row r="12">
@@ -3100,7 +3100,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D12" t="n">
         <v>99</v>
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14">
@@ -3128,7 +3128,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D14" t="n">
         <v>47</v>
@@ -3142,7 +3142,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D15" t="n">
         <v>34</v>
@@ -3156,7 +3156,7 @@
         <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D16" t="n">
         <v>20</v>
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2899</v>
+        <v>2659</v>
       </c>
       <c r="C2" t="n">
-        <v>4336</v>
+        <v>2377</v>
       </c>
       <c r="D2" t="n">
-        <v>10793</v>
+        <v>11555</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3153</v>
+        <v>3167</v>
       </c>
       <c r="C3" t="n">
-        <v>4402</v>
+        <v>3661</v>
       </c>
       <c r="D3" t="n">
-        <v>15255</v>
+        <v>11613</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3335</v>
+        <v>3349</v>
       </c>
       <c r="C4" t="n">
-        <v>5651</v>
+        <v>4581</v>
       </c>
       <c r="D4" t="n">
-        <v>13175</v>
+        <v>10386</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2759</v>
+        <v>2630</v>
       </c>
       <c r="C5" t="n">
-        <v>7465</v>
+        <v>6036</v>
       </c>
       <c r="D5" t="n">
-        <v>6423</v>
+        <v>5774</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1512</v>
+        <v>1394</v>
       </c>
       <c r="C6" t="n">
-        <v>6721</v>
+        <v>6388</v>
       </c>
       <c r="D6" t="n">
-        <v>2039</v>
+        <v>2062</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>359</v>
+        <v>306</v>
       </c>
       <c r="C7" t="n">
-        <v>4026</v>
+        <v>4632</v>
       </c>
       <c r="D7" t="n">
-        <v>755</v>
+        <v>757</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="C8" t="n">
-        <v>1895</v>
+        <v>2341</v>
       </c>
       <c r="D8" t="n">
-        <v>410</v>
+        <v>430</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>630</v>
+        <v>743</v>
       </c>
       <c r="D9" t="n">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="D10" t="n">
-        <v>177</v>
+        <v>180</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D11" t="n">
-        <v>138</v>
+        <v>135</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D12" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14">
@@ -3439,7 +3439,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D14" t="n">
         <v>37</v>
@@ -3453,7 +3453,7 @@
         <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D15" t="n">
         <v>19</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4050</v>
+        <v>4505</v>
       </c>
       <c r="C2" t="n">
-        <v>13637</v>
+        <v>4768</v>
       </c>
       <c r="D2" t="n">
-        <v>13319</v>
+        <v>14397</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2577</v>
+        <v>2508</v>
       </c>
       <c r="C3" t="n">
-        <v>3927</v>
+        <v>2807</v>
       </c>
       <c r="D3" t="n">
-        <v>13743</v>
+        <v>10955</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2842</v>
+        <v>2853</v>
       </c>
       <c r="C4" t="n">
-        <v>5005</v>
+        <v>4044</v>
       </c>
       <c r="D4" t="n">
-        <v>13074</v>
+        <v>10147</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2725</v>
+        <v>2651</v>
       </c>
       <c r="C5" t="n">
-        <v>6578</v>
+        <v>5295</v>
       </c>
       <c r="D5" t="n">
-        <v>7135</v>
+        <v>6262</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1796</v>
+        <v>1692</v>
       </c>
       <c r="C6" t="n">
-        <v>6950</v>
+        <v>6252</v>
       </c>
       <c r="D6" t="n">
-        <v>2540</v>
+        <v>2534</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>639</v>
+        <v>582</v>
       </c>
       <c r="C7" t="n">
-        <v>5028</v>
+        <v>5301</v>
       </c>
       <c r="D7" t="n">
-        <v>910</v>
+        <v>915</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>131</v>
+        <v>112</v>
       </c>
       <c r="C8" t="n">
-        <v>2664</v>
+        <v>3193</v>
       </c>
       <c r="D8" t="n">
-        <v>446</v>
+        <v>464</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C9" t="n">
-        <v>1038</v>
+        <v>1275</v>
       </c>
       <c r="D9" t="n">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C10" t="n">
-        <v>354</v>
+        <v>398</v>
       </c>
       <c r="D10" t="n">
-        <v>185</v>
+        <v>191</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D11" t="n">
-        <v>141</v>
+        <v>137</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D12" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D13" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14">
@@ -3750,7 +3750,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D14" t="n">
         <v>38</v>
@@ -3764,7 +3764,7 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D15" t="n">
         <v>18</v>
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7801</v>
+        <v>5041</v>
       </c>
       <c r="C2" t="n">
-        <v>7669</v>
+        <v>8776</v>
       </c>
       <c r="D2" t="n">
-        <v>6975</v>
+        <v>13181</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2900</v>
+        <v>3188</v>
       </c>
       <c r="C2" t="n">
-        <v>7745</v>
+        <v>2670</v>
       </c>
       <c r="D2" t="n">
-        <v>9803</v>
+        <v>10596</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3447</v>
+        <v>3444</v>
       </c>
       <c r="C3" t="n">
-        <v>6519</v>
+        <v>3515</v>
       </c>
       <c r="D3" t="n">
-        <v>14924</v>
+        <v>12120</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3967</v>
+        <v>3907</v>
       </c>
       <c r="C4" t="n">
-        <v>7240</v>
+        <v>5781</v>
       </c>
       <c r="D4" t="n">
-        <v>13384</v>
+        <v>10502</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1735</v>
+        <v>1661</v>
       </c>
       <c r="C5" t="n">
-        <v>9742</v>
+        <v>8347</v>
       </c>
       <c r="D5" t="n">
-        <v>6381</v>
+        <v>5810</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>590</v>
+        <v>537</v>
       </c>
       <c r="C6" t="n">
-        <v>6289</v>
+        <v>6481</v>
       </c>
       <c r="D6" t="n">
-        <v>2020</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>121</v>
+        <v>103</v>
       </c>
       <c r="C7" t="n">
-        <v>2610</v>
+        <v>3129</v>
       </c>
       <c r="D7" t="n">
-        <v>553</v>
+        <v>580</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C8" t="n">
-        <v>1017</v>
+        <v>1249</v>
       </c>
       <c r="D8" t="n">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>346</v>
+        <v>390</v>
       </c>
       <c r="D9" t="n">
-        <v>181</v>
+        <v>187</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D10" t="n">
-        <v>138</v>
+        <v>134</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D11" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D12" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="13">
@@ -4358,7 +4358,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D13" t="n">
         <v>37</v>
@@ -4372,7 +4372,7 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
         <v>17</v>
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7881</v>
+        <v>6238</v>
       </c>
       <c r="C2" t="n">
-        <v>4398</v>
+        <v>7049</v>
       </c>
       <c r="D2" t="n">
-        <v>15992</v>
+        <v>14523</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3313</v>
+        <v>2142</v>
       </c>
       <c r="C3" t="n">
-        <v>3865</v>
+        <v>4423</v>
       </c>
       <c r="D3" t="n">
-        <v>1811</v>
+        <v>2853</v>
       </c>
     </row>
     <row r="4">
@@ -4554,7 +4554,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C5" t="n">
         <v>381</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C6" t="n">
         <v>459</v>
       </c>
       <c r="D6" t="n">
-        <v>808</v>
+        <v>816</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>350</v>
       </c>
       <c r="D7" t="n">
-        <v>546</v>
+        <v>538</v>
       </c>
     </row>
     <row r="8">
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5738</v>
+        <v>3877</v>
       </c>
       <c r="C2" t="n">
-        <v>2775</v>
+        <v>3992</v>
       </c>
       <c r="D2" t="n">
-        <v>14907</v>
+        <v>21546</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4598</v>
+        <v>3439</v>
       </c>
       <c r="C3" t="n">
-        <v>3593</v>
+        <v>5095</v>
       </c>
       <c r="D3" t="n">
-        <v>4060</v>
+        <v>4603</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1473</v>
+        <v>965</v>
       </c>
       <c r="C4" t="n">
-        <v>2309</v>
+        <v>2636</v>
       </c>
       <c r="D4" t="n">
-        <v>1546</v>
+        <v>1756</v>
       </c>
     </row>
     <row r="5">
@@ -4865,7 +4865,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C5" t="n">
         <v>219</v>
@@ -4885,7 +4885,7 @@
         <v>410</v>
       </c>
       <c r="D6" t="n">
-        <v>853</v>
+        <v>859</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C7" t="n">
         <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>589</v>
+        <v>584</v>
       </c>
     </row>
     <row r="8">
@@ -4913,7 +4913,7 @@
         <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="9">
@@ -4938,7 +4938,7 @@
         <v>63</v>
       </c>
       <c r="C10" t="n">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="D10" t="n">
         <v>352</v>
@@ -4952,7 +4952,7 @@
         <v>43</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D11" t="n">
         <v>270</v>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5068</v>
+        <v>6226</v>
       </c>
       <c r="C2" t="n">
-        <v>5064</v>
+        <v>6132</v>
       </c>
       <c r="D2" t="n">
-        <v>23680</v>
+        <v>18690</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4247</v>
+        <v>3014</v>
       </c>
       <c r="C3" t="n">
-        <v>2724</v>
+        <v>3889</v>
       </c>
       <c r="D3" t="n">
-        <v>5503</v>
+        <v>6982</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2572</v>
+        <v>1871</v>
       </c>
       <c r="C4" t="n">
-        <v>2988</v>
+        <v>3973</v>
       </c>
       <c r="D4" t="n">
-        <v>1981</v>
+        <v>2249</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>664</v>
+        <v>448</v>
       </c>
       <c r="C5" t="n">
-        <v>1358</v>
+        <v>1537</v>
       </c>
       <c r="D5" t="n">
-        <v>1213</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C6" t="n">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="D6" t="n">
-        <v>903</v>
+        <v>908</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="D7" t="n">
-        <v>623</v>
+        <v>626</v>
       </c>
     </row>
     <row r="8">
@@ -5224,7 +5224,7 @@
         <v>358</v>
       </c>
       <c r="D8" t="n">
-        <v>462</v>
+        <v>454</v>
       </c>
     </row>
     <row r="9">
@@ -5238,7 +5238,7 @@
         <v>268</v>
       </c>
       <c r="D9" t="n">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="10">
@@ -5249,7 +5249,7 @@
         <v>67</v>
       </c>
       <c r="C10" t="n">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="D10" t="n">
         <v>346</v>
@@ -5263,7 +5263,7 @@
         <v>47</v>
       </c>
       <c r="C11" t="n">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D11" t="n">
         <v>280</v>
@@ -5277,10 +5277,10 @@
         <v>31</v>
       </c>
       <c r="C12" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D12" t="n">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="13">
@@ -5294,7 +5294,7 @@
         <v>116</v>
       </c>
       <c r="D13" t="n">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="14">
@@ -5305,7 +5305,7 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D14" t="n">
         <v>148</v>
@@ -5319,7 +5319,7 @@
         <v>13</v>
       </c>
       <c r="C15" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D15" t="n">
         <v>120</v>
@@ -5375,7 +5375,7 @@
         <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D19" t="n">
         <v>41</v>
@@ -5406,7 +5406,7 @@
         <v>122</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6025</v>
+        <v>6475</v>
       </c>
       <c r="C2" t="n">
-        <v>5932</v>
+        <v>5649</v>
       </c>
       <c r="D2" t="n">
-        <v>18968</v>
+        <v>27417</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3823</v>
+        <v>3701</v>
       </c>
       <c r="C3" t="n">
-        <v>3419</v>
+        <v>4389</v>
       </c>
       <c r="D3" t="n">
-        <v>7878</v>
+        <v>8270</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2905</v>
+        <v>2083</v>
       </c>
       <c r="C4" t="n">
-        <v>2755</v>
+        <v>3845</v>
       </c>
       <c r="D4" t="n">
-        <v>2563</v>
+        <v>3043</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1329</v>
+        <v>949</v>
       </c>
       <c r="C5" t="n">
-        <v>2190</v>
+        <v>2753</v>
       </c>
       <c r="D5" t="n">
-        <v>1297</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>348</v>
+        <v>261</v>
       </c>
       <c r="C6" t="n">
-        <v>835</v>
+        <v>928</v>
       </c>
       <c r="D6" t="n">
-        <v>944</v>
+        <v>954</v>
       </c>
     </row>
     <row r="7">
@@ -5521,7 +5521,7 @@
         <v>354</v>
       </c>
       <c r="D7" t="n">
-        <v>657</v>
+        <v>660</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C8" t="n">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="D8" t="n">
-        <v>484</v>
+        <v>478</v>
       </c>
     </row>
     <row r="9">
@@ -5549,7 +5549,7 @@
         <v>310</v>
       </c>
       <c r="D9" t="n">
-        <v>378</v>
+        <v>376</v>
       </c>
     </row>
     <row r="10">
@@ -5557,10 +5557,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C10" t="n">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="D10" t="n">
         <v>346</v>
@@ -5571,7 +5571,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C11" t="n">
         <v>187</v>
@@ -5588,10 +5588,10 @@
         <v>34</v>
       </c>
       <c r="C12" t="n">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D12" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="13">
@@ -5605,7 +5605,7 @@
         <v>128</v>
       </c>
       <c r="D13" t="n">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="14">
@@ -5644,7 +5644,7 @@
         <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D16" t="n">
         <v>100</v>
@@ -5717,7 +5717,7 @@
         <v>137</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6712</v>
+        <v>6722</v>
       </c>
       <c r="C2" t="n">
-        <v>7007</v>
+        <v>8599</v>
       </c>
       <c r="D2" t="n">
-        <v>32842</v>
+        <v>25618</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3602</v>
+        <v>3663</v>
       </c>
       <c r="C3" t="n">
-        <v>3852</v>
+        <v>4123</v>
       </c>
       <c r="D3" t="n">
-        <v>8476</v>
+        <v>9970</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2076</v>
+        <v>1780</v>
       </c>
       <c r="C4" t="n">
-        <v>2535</v>
+        <v>3395</v>
       </c>
       <c r="D4" t="n">
-        <v>2993</v>
+        <v>3405</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1105</v>
+        <v>796</v>
       </c>
       <c r="C5" t="n">
-        <v>1815</v>
+        <v>2402</v>
       </c>
       <c r="D5" t="n">
-        <v>1206</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>400</v>
+        <v>284</v>
       </c>
       <c r="C6" t="n">
-        <v>1017</v>
+        <v>1244</v>
       </c>
       <c r="D6" t="n">
-        <v>764</v>
+        <v>780</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>105</v>
+        <v>88</v>
       </c>
       <c r="C7" t="n">
-        <v>379</v>
+        <v>403</v>
       </c>
       <c r="D7" t="n">
-        <v>511</v>
+        <v>514</v>
       </c>
     </row>
     <row r="8">
@@ -5846,7 +5846,7 @@
         <v>223</v>
       </c>
       <c r="D8" t="n">
-        <v>363</v>
+        <v>360</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D9" t="n">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="10">
@@ -5868,10 +5868,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C10" t="n">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D10" t="n">
         <v>237</v>
@@ -5885,7 +5885,7 @@
         <v>21</v>
       </c>
       <c r="C11" t="n">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D11" t="n">
         <v>194</v>
@@ -5899,7 +5899,7 @@
         <v>14</v>
       </c>
       <c r="C12" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D12" t="n">
         <v>148</v>
@@ -5930,7 +5930,7 @@
         <v>57</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="15">
@@ -5941,7 +5941,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D15" t="n">
         <v>79</v>
@@ -5969,7 +5969,7 @@
         <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D17" t="n">
         <v>50</v>
@@ -6011,7 +6011,7 @@
         <v>2</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>15</v>
@@ -6028,7 +6028,7 @@
         <v>75</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6951</v>
+        <v>5971</v>
       </c>
       <c r="C2" t="n">
-        <v>5454</v>
+        <v>7116</v>
       </c>
       <c r="D2" t="n">
-        <v>28607</v>
+        <v>23423</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4288</v>
+        <v>4316</v>
       </c>
       <c r="C3" t="n">
-        <v>4918</v>
+        <v>5798</v>
       </c>
       <c r="D3" t="n">
-        <v>12127</v>
+        <v>11865</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2475</v>
+        <v>2397</v>
       </c>
       <c r="C4" t="n">
-        <v>3291</v>
+        <v>3764</v>
       </c>
       <c r="D4" t="n">
-        <v>4060</v>
+        <v>4592</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1430</v>
+        <v>1141</v>
       </c>
       <c r="C5" t="n">
-        <v>2205</v>
+        <v>2910</v>
       </c>
       <c r="D5" t="n">
-        <v>1529</v>
+        <v>1685</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>702</v>
+        <v>504</v>
       </c>
       <c r="C6" t="n">
-        <v>1464</v>
+        <v>1895</v>
       </c>
       <c r="D6" t="n">
-        <v>830</v>
+        <v>861</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>228</v>
+        <v>169</v>
       </c>
       <c r="C7" t="n">
-        <v>741</v>
+        <v>880</v>
       </c>
       <c r="D7" t="n">
-        <v>555</v>
+        <v>560</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="C8" t="n">
-        <v>306</v>
+        <v>321</v>
       </c>
       <c r="D8" t="n">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="9">
@@ -6171,7 +6171,7 @@
         <v>211</v>
       </c>
       <c r="D9" t="n">
-        <v>281</v>
+        <v>278</v>
       </c>
     </row>
     <row r="10">
@@ -6179,10 +6179,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C10" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D10" t="n">
         <v>240</v>
@@ -6224,7 +6224,7 @@
         <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D13" t="n">
         <v>120</v>
@@ -6235,7 +6235,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
         <v>64</v>
@@ -6252,7 +6252,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D15" t="n">
         <v>79</v>
@@ -6280,7 +6280,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D17" t="n">
         <v>51</v>
@@ -6322,7 +6322,7 @@
         <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -6336,10 +6336,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5681</v>
+        <v>4771</v>
       </c>
       <c r="C2" t="n">
-        <v>6807</v>
+        <v>7774</v>
       </c>
       <c r="D2" t="n">
-        <v>32605</v>
+        <v>21755</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4607</v>
+        <v>4216</v>
       </c>
       <c r="C3" t="n">
-        <v>4506</v>
+        <v>5640</v>
       </c>
       <c r="D3" t="n">
-        <v>13890</v>
+        <v>12860</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2923</v>
+        <v>2863</v>
       </c>
       <c r="C4" t="n">
-        <v>4159</v>
+        <v>4837</v>
       </c>
       <c r="D4" t="n">
-        <v>5446</v>
+        <v>5848</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1712</v>
+        <v>1549</v>
       </c>
       <c r="C5" t="n">
-        <v>2763</v>
+        <v>3288</v>
       </c>
       <c r="D5" t="n">
-        <v>1968</v>
+        <v>2147</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>977</v>
+        <v>741</v>
       </c>
       <c r="C6" t="n">
-        <v>1845</v>
+        <v>2418</v>
       </c>
       <c r="D6" t="n">
-        <v>945</v>
+        <v>999</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>409</v>
+        <v>298</v>
       </c>
       <c r="C7" t="n">
-        <v>1116</v>
+        <v>1416</v>
       </c>
       <c r="D7" t="n">
-        <v>592</v>
+        <v>601</v>
       </c>
     </row>
     <row r="8">
@@ -6462,10 +6462,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>132</v>
+        <v>102</v>
       </c>
       <c r="C8" t="n">
-        <v>531</v>
+        <v>605</v>
       </c>
       <c r="D8" t="n">
         <v>411</v>
@@ -6476,10 +6476,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C9" t="n">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="D9" t="n">
         <v>292</v>
@@ -6493,10 +6493,10 @@
         <v>36</v>
       </c>
       <c r="C10" t="n">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="D10" t="n">
-        <v>244</v>
+        <v>241</v>
       </c>
     </row>
     <row r="11">
@@ -6507,7 +6507,7 @@
         <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D11" t="n">
         <v>203</v>
@@ -6532,10 +6532,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D13" t="n">
         <v>123</v>
@@ -6549,7 +6549,7 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
         <v>100</v>
@@ -6563,7 +6563,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D15" t="n">
         <v>79</v>
@@ -6591,10 +6591,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -6605,10 +6605,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -6633,7 +6633,7 @@
         <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -6647,10 +6647,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_population_iteration_40_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_40_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5499</v>
+        <v>6239</v>
       </c>
       <c r="C2" t="n">
-        <v>7586</v>
+        <v>11524</v>
       </c>
       <c r="D2" t="n">
-        <v>17976</v>
+        <v>24275</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3731</v>
+        <v>3718</v>
       </c>
       <c r="C3" t="n">
-        <v>5857</v>
+        <v>4931</v>
       </c>
       <c r="D3" t="n">
-        <v>13430</v>
+        <v>14827</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2982</v>
+        <v>2666</v>
       </c>
       <c r="C4" t="n">
-        <v>5160</v>
+        <v>6261</v>
       </c>
       <c r="D4" t="n">
-        <v>6825</v>
+        <v>7048</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1889</v>
+        <v>1747</v>
       </c>
       <c r="C5" t="n">
-        <v>4007</v>
+        <v>4461</v>
       </c>
       <c r="D5" t="n">
-        <v>2721</v>
+        <v>2628</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1019</v>
+        <v>1035</v>
       </c>
       <c r="C6" t="n">
-        <v>2794</v>
+        <v>2644</v>
       </c>
       <c r="D6" t="n">
-        <v>1162</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>445</v>
+        <v>483</v>
       </c>
       <c r="C7" t="n">
-        <v>1906</v>
+        <v>1805</v>
       </c>
       <c r="D7" t="n">
-        <v>661</v>
+        <v>643</v>
       </c>
     </row>
     <row r="8">
@@ -864,10 +864,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="C8" t="n">
-        <v>986</v>
+        <v>917</v>
       </c>
       <c r="D8" t="n">
         <v>432</v>
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C9" t="n">
-        <v>415</v>
+        <v>381</v>
       </c>
       <c r="D9" t="n">
-        <v>307</v>
+        <v>310</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C10" t="n">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="D10" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="11">
@@ -909,7 +909,7 @@
         <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D11" t="n">
         <v>206</v>
@@ -937,7 +937,7 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
         <v>124</v>
@@ -951,7 +951,7 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D14" t="n">
         <v>101</v>
@@ -965,7 +965,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D15" t="n">
         <v>79</v>
@@ -979,7 +979,7 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D16" t="n">
         <v>65</v>
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1049,10 +1049,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8912</v>
+        <v>6730</v>
       </c>
       <c r="C2" t="n">
-        <v>5001</v>
+        <v>11326</v>
       </c>
       <c r="D2" t="n">
-        <v>23680</v>
+        <v>29259</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3691</v>
+        <v>3933</v>
       </c>
       <c r="C3" t="n">
-        <v>5845</v>
+        <v>6976</v>
       </c>
       <c r="D3" t="n">
-        <v>13145</v>
+        <v>15115</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2834</v>
+        <v>2693</v>
       </c>
       <c r="C4" t="n">
-        <v>5337</v>
+        <v>5432</v>
       </c>
       <c r="D4" t="n">
-        <v>7629</v>
+        <v>8103</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2106</v>
+        <v>1893</v>
       </c>
       <c r="C5" t="n">
-        <v>4466</v>
+        <v>5214</v>
       </c>
       <c r="D5" t="n">
-        <v>3308</v>
+        <v>3201</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1264</v>
+        <v>1222</v>
       </c>
       <c r="C6" t="n">
-        <v>3286</v>
+        <v>3412</v>
       </c>
       <c r="D6" t="n">
-        <v>1374</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>616</v>
+        <v>649</v>
       </c>
       <c r="C7" t="n">
-        <v>2305</v>
+        <v>2182</v>
       </c>
       <c r="D7" t="n">
-        <v>732</v>
+        <v>696</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>253</v>
+        <v>268</v>
       </c>
       <c r="C8" t="n">
-        <v>1372</v>
+        <v>1290</v>
       </c>
       <c r="D8" t="n">
-        <v>461</v>
+        <v>458</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="C9" t="n">
-        <v>655</v>
+        <v>606</v>
       </c>
       <c r="D9" t="n">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="10">
@@ -1206,10 +1206,10 @@
         <v>44</v>
       </c>
       <c r="C10" t="n">
-        <v>296</v>
+        <v>280</v>
       </c>
       <c r="D10" t="n">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="11">
@@ -1217,10 +1217,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C11" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D11" t="n">
         <v>206</v>
@@ -1245,7 +1245,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C13" t="n">
         <v>109</v>
@@ -1276,7 +1276,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
         <v>79</v>
@@ -1290,7 +1290,7 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D16" t="n">
         <v>65</v>
@@ -1318,7 +1318,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
         <v>39</v>
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1360,10 +1360,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9352</v>
+        <v>8168</v>
       </c>
       <c r="C2" t="n">
-        <v>4807</v>
+        <v>8827</v>
       </c>
       <c r="D2" t="n">
-        <v>22960</v>
+        <v>29224</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4658</v>
+        <v>4123</v>
       </c>
       <c r="C3" t="n">
-        <v>4870</v>
+        <v>7851</v>
       </c>
       <c r="D3" t="n">
-        <v>13631</v>
+        <v>16078</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2716</v>
+        <v>2718</v>
       </c>
       <c r="C4" t="n">
-        <v>5399</v>
+        <v>5933</v>
       </c>
       <c r="D4" t="n">
-        <v>8244</v>
+        <v>8788</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2138</v>
+        <v>1985</v>
       </c>
       <c r="C5" t="n">
-        <v>4749</v>
+        <v>5147</v>
       </c>
       <c r="D5" t="n">
-        <v>3797</v>
+        <v>3778</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1459</v>
+        <v>1357</v>
       </c>
       <c r="C6" t="n">
-        <v>3711</v>
+        <v>4125</v>
       </c>
       <c r="D6" t="n">
-        <v>1634</v>
+        <v>1568</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>790</v>
+        <v>785</v>
       </c>
       <c r="C7" t="n">
-        <v>2707</v>
+        <v>2653</v>
       </c>
       <c r="D7" t="n">
-        <v>805</v>
+        <v>766</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>346</v>
+        <v>366</v>
       </c>
       <c r="C8" t="n">
-        <v>1723</v>
+        <v>1626</v>
       </c>
       <c r="D8" t="n">
-        <v>493</v>
+        <v>485</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="C9" t="n">
-        <v>922</v>
+        <v>867</v>
       </c>
       <c r="D9" t="n">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C10" t="n">
-        <v>429</v>
+        <v>395</v>
       </c>
       <c r="D10" t="n">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C11" t="n">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="12">
@@ -1545,7 +1545,7 @@
         <v>19</v>
       </c>
       <c r="C12" t="n">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D12" t="n">
         <v>167</v>
@@ -1559,7 +1559,7 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D13" t="n">
         <v>126</v>
@@ -1570,10 +1570,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D14" t="n">
         <v>103</v>
@@ -1601,7 +1601,7 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D16" t="n">
         <v>65</v>
@@ -1615,7 +1615,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1671,10 +1671,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8483</v>
+        <v>7456</v>
       </c>
       <c r="C2" t="n">
-        <v>3230</v>
+        <v>6002</v>
       </c>
       <c r="D2" t="n">
-        <v>18891</v>
+        <v>24150</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5290</v>
+        <v>4915</v>
       </c>
       <c r="C3" t="n">
-        <v>7467</v>
+        <v>11045</v>
       </c>
       <c r="D3" t="n">
-        <v>15015</v>
+        <v>17362</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1975</v>
+        <v>1834</v>
       </c>
       <c r="C4" t="n">
-        <v>7565</v>
+        <v>8187</v>
       </c>
       <c r="D4" t="n">
-        <v>8048</v>
+        <v>8348</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1348</v>
+        <v>1253</v>
       </c>
       <c r="C5" t="n">
-        <v>3636</v>
+        <v>4042</v>
       </c>
       <c r="D5" t="n">
-        <v>2658</v>
+        <v>2552</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>729</v>
+        <v>725</v>
       </c>
       <c r="C6" t="n">
-        <v>2652</v>
+        <v>2599</v>
       </c>
       <c r="D6" t="n">
-        <v>788</v>
+        <v>750</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>319</v>
+        <v>338</v>
       </c>
       <c r="C7" t="n">
-        <v>1688</v>
+        <v>1593</v>
       </c>
       <c r="D7" t="n">
-        <v>483</v>
+        <v>475</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="C8" t="n">
-        <v>903</v>
+        <v>849</v>
       </c>
       <c r="D8" t="n">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C9" t="n">
-        <v>420</v>
+        <v>387</v>
       </c>
       <c r="D9" t="n">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C10" t="n">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="D10" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="11">
@@ -1842,7 +1842,7 @@
         <v>17</v>
       </c>
       <c r="C11" t="n">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D11" t="n">
         <v>163</v>
@@ -1856,7 +1856,7 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D12" t="n">
         <v>123</v>
@@ -1867,10 +1867,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C13" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
         <v>100</v>
@@ -1898,7 +1898,7 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D15" t="n">
         <v>63</v>
@@ -1912,7 +1912,7 @@
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D16" t="n">
         <v>50</v>
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D19" t="n">
         <v>15</v>
@@ -1968,10 +1968,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4882</v>
+        <v>4623</v>
       </c>
       <c r="C2" t="n">
-        <v>2258</v>
+        <v>2966</v>
       </c>
       <c r="D2" t="n">
-        <v>13603</v>
+        <v>16912</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5712</v>
+        <v>5149</v>
       </c>
       <c r="C3" t="n">
-        <v>4999</v>
+        <v>7962</v>
       </c>
       <c r="D3" t="n">
-        <v>14677</v>
+        <v>17285</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2822</v>
+        <v>2595</v>
       </c>
       <c r="C4" t="n">
-        <v>7579</v>
+        <v>9569</v>
       </c>
       <c r="D4" t="n">
-        <v>9027</v>
+        <v>9639</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1508</v>
+        <v>1397</v>
       </c>
       <c r="C5" t="n">
-        <v>5394</v>
+        <v>5862</v>
       </c>
       <c r="D5" t="n">
-        <v>3300</v>
+        <v>3246</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>880</v>
+        <v>854</v>
       </c>
       <c r="C6" t="n">
-        <v>3162</v>
+        <v>3230</v>
       </c>
       <c r="D6" t="n">
-        <v>981</v>
+        <v>935</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>299</v>
+        <v>318</v>
       </c>
       <c r="C7" t="n">
-        <v>2084</v>
+        <v>2008</v>
       </c>
       <c r="D7" t="n">
-        <v>527</v>
+        <v>517</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="C8" t="n">
-        <v>1176</v>
+        <v>1099</v>
       </c>
       <c r="D8" t="n">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C9" t="n">
-        <v>477</v>
+        <v>435</v>
       </c>
       <c r="D9" t="n">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="10">
@@ -2139,7 +2139,7 @@
         <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="D10" t="n">
         <v>211</v>
@@ -2164,7 +2164,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
         <v>97</v>
@@ -2195,7 +2195,7 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D14" t="n">
         <v>61</v>
@@ -2209,7 +2209,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D15" t="n">
         <v>49</v>
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D18" t="n">
         <v>14</v>
@@ -2265,10 +2265,10 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5945</v>
+        <v>5653</v>
       </c>
       <c r="C2" t="n">
-        <v>8077</v>
+        <v>10507</v>
       </c>
       <c r="D2" t="n">
-        <v>13407</v>
+        <v>17560</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4502</v>
+        <v>4178</v>
       </c>
       <c r="C3" t="n">
-        <v>3260</v>
+        <v>4979</v>
       </c>
       <c r="D3" t="n">
-        <v>13512</v>
+        <v>16072</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3486</v>
+        <v>3147</v>
       </c>
       <c r="C4" t="n">
-        <v>6133</v>
+        <v>8583</v>
       </c>
       <c r="D4" t="n">
-        <v>9728</v>
+        <v>10593</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1839</v>
+        <v>1688</v>
       </c>
       <c r="C5" t="n">
-        <v>6330</v>
+        <v>7483</v>
       </c>
       <c r="D5" t="n">
-        <v>4134</v>
+        <v>4129</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1060</v>
+        <v>1001</v>
       </c>
       <c r="C6" t="n">
-        <v>4189</v>
+        <v>4417</v>
       </c>
       <c r="D6" t="n">
-        <v>1324</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="C7" t="n">
-        <v>2578</v>
+        <v>2553</v>
       </c>
       <c r="D7" t="n">
-        <v>588</v>
+        <v>569</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="C8" t="n">
-        <v>1560</v>
+        <v>1474</v>
       </c>
       <c r="D8" t="n">
-        <v>362</v>
+        <v>357</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C9" t="n">
-        <v>748</v>
+        <v>686</v>
       </c>
       <c r="D9" t="n">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="10">
@@ -2450,10 +2450,10 @@
         <v>19</v>
       </c>
       <c r="C10" t="n">
-        <v>322</v>
+        <v>304</v>
       </c>
       <c r="D10" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="11">
@@ -2464,7 +2464,7 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D11" t="n">
         <v>170</v>
@@ -2475,10 +2475,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D12" t="n">
         <v>133</v>
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14">
@@ -2506,7 +2506,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
         <v>63</v>
@@ -2520,7 +2520,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D15" t="n">
         <v>48</v>
@@ -2551,7 +2551,7 @@
         <v>31</v>
       </c>
       <c r="D17" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="18">
@@ -2562,7 +2562,7 @@
         <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D18" t="n">
         <v>13</v>
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3465</v>
+        <v>3327</v>
       </c>
       <c r="C2" t="n">
-        <v>3697</v>
+        <v>4912</v>
       </c>
       <c r="D2" t="n">
-        <v>9242</v>
+        <v>12259</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4687</v>
+        <v>4408</v>
       </c>
       <c r="C3" t="n">
-        <v>4812</v>
+        <v>6685</v>
       </c>
       <c r="D3" t="n">
-        <v>13175</v>
+        <v>15866</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3868</v>
+        <v>3455</v>
       </c>
       <c r="C4" t="n">
-        <v>5628</v>
+        <v>8052</v>
       </c>
       <c r="D4" t="n">
-        <v>10262</v>
+        <v>11292</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1915</v>
+        <v>1765</v>
       </c>
       <c r="C5" t="n">
-        <v>7169</v>
+        <v>8896</v>
       </c>
       <c r="D5" t="n">
-        <v>4484</v>
+        <v>4364</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>869</v>
+        <v>832</v>
       </c>
       <c r="C6" t="n">
-        <v>5149</v>
+        <v>5253</v>
       </c>
       <c r="D6" t="n">
-        <v>1293</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="C7" t="n">
-        <v>2782</v>
+        <v>2673</v>
       </c>
       <c r="D7" t="n">
-        <v>590</v>
+        <v>572</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C8" t="n">
-        <v>1222</v>
+        <v>1120</v>
       </c>
       <c r="D8" t="n">
-        <v>383</v>
+        <v>377</v>
       </c>
     </row>
     <row r="9">
@@ -2747,10 +2747,10 @@
         <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>315</v>
+        <v>297</v>
       </c>
       <c r="D9" t="n">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="10">
@@ -2761,7 +2761,7 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D10" t="n">
         <v>166</v>
@@ -2772,10 +2772,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D11" t="n">
         <v>130</v>
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D12" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="13">
@@ -2803,7 +2803,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D13" t="n">
         <v>61</v>
@@ -2817,7 +2817,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D14" t="n">
         <v>47</v>
@@ -2848,7 +2848,7 @@
         <v>30</v>
       </c>
       <c r="D16" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17">
@@ -2859,7 +2859,7 @@
         <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D17" t="n">
         <v>12</v>
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3733</v>
+        <v>3551</v>
       </c>
       <c r="C2" t="n">
-        <v>4342</v>
+        <v>8535</v>
       </c>
       <c r="D2" t="n">
-        <v>15915</v>
+        <v>12466</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3560</v>
+        <v>3382</v>
       </c>
       <c r="C3" t="n">
-        <v>3771</v>
+        <v>5237</v>
       </c>
       <c r="D3" t="n">
-        <v>11754</v>
+        <v>14461</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3673</v>
+        <v>3378</v>
       </c>
       <c r="C4" t="n">
-        <v>5165</v>
+        <v>7318</v>
       </c>
       <c r="D4" t="n">
-        <v>10425</v>
+        <v>11651</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2404</v>
+        <v>2155</v>
       </c>
       <c r="C5" t="n">
-        <v>6378</v>
+        <v>8423</v>
       </c>
       <c r="D5" t="n">
-        <v>5235</v>
+        <v>5228</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1162</v>
+        <v>1066</v>
       </c>
       <c r="C6" t="n">
-        <v>6023</v>
+        <v>6761</v>
       </c>
       <c r="D6" t="n">
-        <v>1748</v>
+        <v>1638</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>325</v>
+        <v>315</v>
       </c>
       <c r="C7" t="n">
-        <v>3809</v>
+        <v>3709</v>
       </c>
       <c r="D7" t="n">
-        <v>673</v>
+        <v>656</v>
       </c>
     </row>
     <row r="8">
@@ -3044,10 +3044,10 @@
         <v>67</v>
       </c>
       <c r="C8" t="n">
-        <v>1826</v>
+        <v>1715</v>
       </c>
       <c r="D8" t="n">
-        <v>407</v>
+        <v>397</v>
       </c>
     </row>
     <row r="9">
@@ -3058,10 +3058,10 @@
         <v>21</v>
       </c>
       <c r="C9" t="n">
-        <v>626</v>
+        <v>560</v>
       </c>
       <c r="D9" t="n">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="10">
@@ -3072,10 +3072,10 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="D10" t="n">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="11">
@@ -3083,10 +3083,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D11" t="n">
         <v>134</v>
@@ -3100,7 +3100,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D12" t="n">
         <v>99</v>
@@ -3128,7 +3128,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D14" t="n">
         <v>47</v>
@@ -3145,7 +3145,7 @@
         <v>37</v>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="16">
@@ -3156,7 +3156,7 @@
         <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D16" t="n">
         <v>20</v>
@@ -3173,7 +3173,7 @@
         <v>72</v>
       </c>
       <c r="D17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D18" t="n">
         <v>2</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2659</v>
+        <v>2463</v>
       </c>
       <c r="C2" t="n">
-        <v>2377</v>
+        <v>4711</v>
       </c>
       <c r="D2" t="n">
-        <v>11555</v>
+        <v>9278</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3167</v>
+        <v>3011</v>
       </c>
       <c r="C3" t="n">
-        <v>3661</v>
+        <v>5920</v>
       </c>
       <c r="D3" t="n">
-        <v>11613</v>
+        <v>13573</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3349</v>
+        <v>3109</v>
       </c>
       <c r="C4" t="n">
-        <v>4581</v>
+        <v>6537</v>
       </c>
       <c r="D4" t="n">
-        <v>10386</v>
+        <v>11759</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2630</v>
+        <v>2385</v>
       </c>
       <c r="C5" t="n">
-        <v>6036</v>
+        <v>8178</v>
       </c>
       <c r="D5" t="n">
-        <v>5774</v>
+        <v>5797</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1394</v>
+        <v>1247</v>
       </c>
       <c r="C6" t="n">
-        <v>6388</v>
+        <v>7542</v>
       </c>
       <c r="D6" t="n">
-        <v>2062</v>
+        <v>1976</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>306</v>
+        <v>284</v>
       </c>
       <c r="C7" t="n">
-        <v>4632</v>
+        <v>4679</v>
       </c>
       <c r="D7" t="n">
-        <v>757</v>
+        <v>728</v>
       </c>
     </row>
     <row r="8">
@@ -3355,10 +3355,10 @@
         <v>55</v>
       </c>
       <c r="C8" t="n">
-        <v>2341</v>
+        <v>2186</v>
       </c>
       <c r="D8" t="n">
-        <v>430</v>
+        <v>409</v>
       </c>
     </row>
     <row r="9">
@@ -3369,10 +3369,10 @@
         <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>743</v>
+        <v>636</v>
       </c>
       <c r="D9" t="n">
-        <v>296</v>
+        <v>294</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="D10" t="n">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="11">
@@ -3397,7 +3397,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="D11" t="n">
         <v>135</v>
@@ -3411,7 +3411,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D12" t="n">
         <v>92</v>
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D13" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14">
@@ -3442,7 +3442,7 @@
         <v>36</v>
       </c>
       <c r="D14" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15">
@@ -3453,7 +3453,7 @@
         <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D15" t="n">
         <v>19</v>
@@ -3470,7 +3470,7 @@
         <v>70</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>1</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4505</v>
+        <v>3227</v>
       </c>
       <c r="C2" t="n">
-        <v>4768</v>
+        <v>10646</v>
       </c>
       <c r="D2" t="n">
-        <v>14397</v>
+        <v>15780</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2508</v>
+        <v>2376</v>
       </c>
       <c r="C3" t="n">
-        <v>2807</v>
+        <v>4897</v>
       </c>
       <c r="D3" t="n">
-        <v>10955</v>
+        <v>12188</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2853</v>
+        <v>2672</v>
       </c>
       <c r="C4" t="n">
-        <v>4044</v>
+        <v>6083</v>
       </c>
       <c r="D4" t="n">
-        <v>10147</v>
+        <v>11662</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2651</v>
+        <v>2394</v>
       </c>
       <c r="C5" t="n">
-        <v>5295</v>
+        <v>7346</v>
       </c>
       <c r="D5" t="n">
-        <v>6262</v>
+        <v>6422</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1692</v>
+        <v>1512</v>
       </c>
       <c r="C6" t="n">
-        <v>6252</v>
+        <v>7796</v>
       </c>
       <c r="D6" t="n">
-        <v>2534</v>
+        <v>2427</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>582</v>
+        <v>519</v>
       </c>
       <c r="C7" t="n">
-        <v>5301</v>
+        <v>5715</v>
       </c>
       <c r="D7" t="n">
-        <v>915</v>
+        <v>867</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="C8" t="n">
-        <v>3193</v>
+        <v>3040</v>
       </c>
       <c r="D8" t="n">
-        <v>464</v>
+        <v>439</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C9" t="n">
-        <v>1275</v>
+        <v>1143</v>
       </c>
       <c r="D9" t="n">
-        <v>307</v>
+        <v>302</v>
       </c>
     </row>
     <row r="10">
@@ -3694,10 +3694,10 @@
         <v>5</v>
       </c>
       <c r="C10" t="n">
-        <v>398</v>
+        <v>350</v>
       </c>
       <c r="D10" t="n">
-        <v>191</v>
+        <v>186</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="D11" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="12">
@@ -3722,7 +3722,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="D12" t="n">
         <v>94</v>
@@ -3739,7 +3739,7 @@
         <v>52</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14">
@@ -3753,7 +3753,7 @@
         <v>38</v>
       </c>
       <c r="D14" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="15">
@@ -3764,7 +3764,7 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
         <v>18</v>
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5041</v>
+        <v>4858</v>
       </c>
       <c r="C2" t="n">
-        <v>8776</v>
+        <v>7138</v>
       </c>
       <c r="D2" t="n">
-        <v>13181</v>
+        <v>7721</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3188</v>
+        <v>2335</v>
       </c>
       <c r="C2" t="n">
-        <v>2670</v>
+        <v>6132</v>
       </c>
       <c r="D2" t="n">
-        <v>10596</v>
+        <v>11740</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3444</v>
+        <v>3147</v>
       </c>
       <c r="C3" t="n">
-        <v>3515</v>
+        <v>6615</v>
       </c>
       <c r="D3" t="n">
-        <v>12120</v>
+        <v>13367</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3907</v>
+        <v>3579</v>
       </c>
       <c r="C4" t="n">
-        <v>5781</v>
+        <v>8637</v>
       </c>
       <c r="D4" t="n">
-        <v>10502</v>
+        <v>11953</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1661</v>
+        <v>1441</v>
       </c>
       <c r="C5" t="n">
-        <v>8347</v>
+        <v>10913</v>
       </c>
       <c r="D5" t="n">
-        <v>5810</v>
+        <v>5813</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>537</v>
+        <v>479</v>
       </c>
       <c r="C6" t="n">
-        <v>6481</v>
+        <v>7052</v>
       </c>
       <c r="D6" t="n">
-        <v>2012</v>
+        <v>1928</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="C7" t="n">
-        <v>3129</v>
+        <v>2979</v>
       </c>
       <c r="D7" t="n">
-        <v>580</v>
+        <v>540</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C8" t="n">
-        <v>1249</v>
+        <v>1120</v>
       </c>
       <c r="D8" t="n">
-        <v>300</v>
+        <v>295</v>
       </c>
     </row>
     <row r="9">
@@ -4302,10 +4302,10 @@
         <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>390</v>
+        <v>343</v>
       </c>
       <c r="D9" t="n">
-        <v>187</v>
+        <v>182</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="D10" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="11">
@@ -4330,7 +4330,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D11" t="n">
         <v>92</v>
@@ -4347,7 +4347,7 @@
         <v>50</v>
       </c>
       <c r="D12" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13">
@@ -4361,7 +4361,7 @@
         <v>37</v>
       </c>
       <c r="D13" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14">
@@ -4372,7 +4372,7 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D14" t="n">
         <v>17</v>
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6238</v>
+        <v>7082</v>
       </c>
       <c r="C2" t="n">
-        <v>7049</v>
+        <v>7387</v>
       </c>
       <c r="D2" t="n">
-        <v>14523</v>
+        <v>11380</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2142</v>
+        <v>2065</v>
       </c>
       <c r="C3" t="n">
-        <v>4423</v>
+        <v>3597</v>
       </c>
       <c r="D3" t="n">
-        <v>2853</v>
+        <v>1936</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>79</v>
       </c>
       <c r="C4" t="n">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D4" t="n">
         <v>1538</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C5" t="n">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="D5" t="n">
         <v>1161</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C6" t="n">
         <v>459</v>
       </c>
       <c r="D6" t="n">
-        <v>816</v>
+        <v>808</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>350</v>
       </c>
       <c r="D7" t="n">
-        <v>538</v>
+        <v>546</v>
       </c>
     </row>
     <row r="8">
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3877</v>
+        <v>5665</v>
       </c>
       <c r="C2" t="n">
-        <v>3992</v>
+        <v>4784</v>
       </c>
       <c r="D2" t="n">
-        <v>21546</v>
+        <v>20683</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3439</v>
+        <v>3751</v>
       </c>
       <c r="C3" t="n">
-        <v>5095</v>
+        <v>5010</v>
       </c>
       <c r="D3" t="n">
-        <v>4603</v>
+        <v>3380</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>965</v>
+        <v>930</v>
       </c>
       <c r="C4" t="n">
-        <v>2636</v>
+        <v>2150</v>
       </c>
       <c r="D4" t="n">
-        <v>1756</v>
+        <v>1571</v>
       </c>
     </row>
     <row r="5">
@@ -4868,10 +4868,10 @@
         <v>125</v>
       </c>
       <c r="C5" t="n">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D5" t="n">
-        <v>1198</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="6">
@@ -4882,10 +4882,10 @@
         <v>185</v>
       </c>
       <c r="C6" t="n">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="D6" t="n">
-        <v>859</v>
+        <v>864</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C7" t="n">
         <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>584</v>
+        <v>589</v>
       </c>
     </row>
     <row r="8">
@@ -4913,7 +4913,7 @@
         <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="9">
@@ -4924,7 +4924,7 @@
         <v>84</v>
       </c>
       <c r="C9" t="n">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="D9" t="n">
         <v>363</v>
@@ -4952,7 +4952,7 @@
         <v>43</v>
       </c>
       <c r="C11" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D11" t="n">
         <v>270</v>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6226</v>
+        <v>5077</v>
       </c>
       <c r="C2" t="n">
-        <v>6132</v>
+        <v>4207</v>
       </c>
       <c r="D2" t="n">
-        <v>18690</v>
+        <v>27693</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3014</v>
+        <v>3850</v>
       </c>
       <c r="C3" t="n">
-        <v>3889</v>
+        <v>4229</v>
       </c>
       <c r="D3" t="n">
-        <v>6982</v>
+        <v>5905</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1871</v>
+        <v>1977</v>
       </c>
       <c r="C4" t="n">
-        <v>3973</v>
+        <v>3725</v>
       </c>
       <c r="D4" t="n">
-        <v>2249</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="C5" t="n">
-        <v>1537</v>
+        <v>1271</v>
       </c>
       <c r="D5" t="n">
-        <v>1251</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C6" t="n">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="D6" t="n">
-        <v>908</v>
+        <v>910</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C7" t="n">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>626</v>
+        <v>625</v>
       </c>
     </row>
     <row r="8">
@@ -5224,7 +5224,7 @@
         <v>358</v>
       </c>
       <c r="D8" t="n">
-        <v>454</v>
+        <v>462</v>
       </c>
     </row>
     <row r="9">
@@ -5235,10 +5235,10 @@
         <v>90</v>
       </c>
       <c r="C9" t="n">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D9" t="n">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="10">
@@ -5249,7 +5249,7 @@
         <v>67</v>
       </c>
       <c r="C10" t="n">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="D10" t="n">
         <v>346</v>
@@ -5263,7 +5263,7 @@
         <v>47</v>
       </c>
       <c r="C11" t="n">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="D11" t="n">
         <v>280</v>
@@ -5277,10 +5277,10 @@
         <v>31</v>
       </c>
       <c r="C12" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D12" t="n">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="13">
@@ -5294,7 +5294,7 @@
         <v>116</v>
       </c>
       <c r="D13" t="n">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="14">
@@ -5305,7 +5305,7 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D14" t="n">
         <v>148</v>
@@ -5319,7 +5319,7 @@
         <v>13</v>
       </c>
       <c r="C15" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D15" t="n">
         <v>120</v>
@@ -5375,7 +5375,7 @@
         <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D19" t="n">
         <v>41</v>
@@ -5406,7 +5406,7 @@
         <v>122</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6475</v>
+        <v>4811</v>
       </c>
       <c r="C2" t="n">
-        <v>5649</v>
+        <v>5979</v>
       </c>
       <c r="D2" t="n">
-        <v>27417</v>
+        <v>24840</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3701</v>
+        <v>3647</v>
       </c>
       <c r="C3" t="n">
-        <v>4389</v>
+        <v>3671</v>
       </c>
       <c r="D3" t="n">
-        <v>8270</v>
+        <v>8801</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2083</v>
+        <v>2468</v>
       </c>
       <c r="C4" t="n">
-        <v>3845</v>
+        <v>3918</v>
       </c>
       <c r="D4" t="n">
-        <v>3043</v>
+        <v>2549</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>949</v>
+        <v>986</v>
       </c>
       <c r="C5" t="n">
-        <v>2753</v>
+        <v>2504</v>
       </c>
       <c r="D5" t="n">
-        <v>1373</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="C6" t="n">
-        <v>928</v>
+        <v>791</v>
       </c>
       <c r="D6" t="n">
-        <v>954</v>
+        <v>948</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C7" t="n">
         <v>354</v>
       </c>
       <c r="D7" t="n">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C8" t="n">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="D8" t="n">
-        <v>478</v>
+        <v>484</v>
       </c>
     </row>
     <row r="9">
@@ -5546,10 +5546,10 @@
         <v>96</v>
       </c>
       <c r="C9" t="n">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D9" t="n">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="10">
@@ -5557,10 +5557,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C10" t="n">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="D10" t="n">
         <v>346</v>
@@ -5571,10 +5571,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C11" t="n">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D11" t="n">
         <v>286</v>
@@ -5588,10 +5588,10 @@
         <v>34</v>
       </c>
       <c r="C12" t="n">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="D12" t="n">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="13">
@@ -5605,7 +5605,7 @@
         <v>128</v>
       </c>
       <c r="D13" t="n">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="14">
@@ -5644,7 +5644,7 @@
         <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D16" t="n">
         <v>100</v>
@@ -5717,7 +5717,7 @@
         <v>137</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6722</v>
+        <v>6082</v>
       </c>
       <c r="C2" t="n">
-        <v>8599</v>
+        <v>12597</v>
       </c>
       <c r="D2" t="n">
-        <v>25618</v>
+        <v>29339</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3663</v>
+        <v>3068</v>
       </c>
       <c r="C3" t="n">
-        <v>4123</v>
+        <v>3973</v>
       </c>
       <c r="D3" t="n">
-        <v>9970</v>
+        <v>9990</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1780</v>
+        <v>1885</v>
       </c>
       <c r="C4" t="n">
-        <v>3395</v>
+        <v>3068</v>
       </c>
       <c r="D4" t="n">
-        <v>3405</v>
+        <v>3153</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>796</v>
+        <v>894</v>
       </c>
       <c r="C5" t="n">
-        <v>2402</v>
+        <v>2375</v>
       </c>
       <c r="D5" t="n">
-        <v>1301</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>284</v>
+        <v>296</v>
       </c>
       <c r="C6" t="n">
-        <v>1244</v>
+        <v>1114</v>
       </c>
       <c r="D6" t="n">
-        <v>780</v>
+        <v>763</v>
       </c>
     </row>
     <row r="7">
@@ -5829,10 +5829,10 @@
         <v>88</v>
       </c>
       <c r="C7" t="n">
-        <v>403</v>
+        <v>360</v>
       </c>
       <c r="D7" t="n">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C8" t="n">
         <v>223</v>
       </c>
       <c r="D8" t="n">
-        <v>360</v>
+        <v>364</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="D9" t="n">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="10">
@@ -5868,10 +5868,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C10" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D10" t="n">
         <v>237</v>
@@ -5885,7 +5885,7 @@
         <v>21</v>
       </c>
       <c r="C11" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D11" t="n">
         <v>194</v>
@@ -5899,7 +5899,7 @@
         <v>14</v>
       </c>
       <c r="C12" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D12" t="n">
         <v>148</v>
@@ -5930,7 +5930,7 @@
         <v>57</v>
       </c>
       <c r="D14" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="15">
@@ -5941,7 +5941,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D15" t="n">
         <v>79</v>
@@ -6011,7 +6011,7 @@
         <v>2</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>15</v>
@@ -6028,7 +6028,7 @@
         <v>75</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5971</v>
+        <v>5424</v>
       </c>
       <c r="C2" t="n">
-        <v>7116</v>
+        <v>7922</v>
       </c>
       <c r="D2" t="n">
-        <v>23423</v>
+        <v>25484</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4316</v>
+        <v>3807</v>
       </c>
       <c r="C3" t="n">
-        <v>5798</v>
+        <v>7822</v>
       </c>
       <c r="D3" t="n">
-        <v>11865</v>
+        <v>12644</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2397</v>
+        <v>2172</v>
       </c>
       <c r="C4" t="n">
-        <v>3764</v>
+        <v>3560</v>
       </c>
       <c r="D4" t="n">
-        <v>4592</v>
+        <v>4501</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1141</v>
+        <v>1232</v>
       </c>
       <c r="C5" t="n">
-        <v>2910</v>
+        <v>2738</v>
       </c>
       <c r="D5" t="n">
-        <v>1685</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>504</v>
+        <v>555</v>
       </c>
       <c r="C6" t="n">
-        <v>1895</v>
+        <v>1826</v>
       </c>
       <c r="D6" t="n">
-        <v>861</v>
+        <v>822</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="C7" t="n">
-        <v>880</v>
+        <v>788</v>
       </c>
       <c r="D7" t="n">
-        <v>560</v>
+        <v>556</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C8" t="n">
-        <v>321</v>
+        <v>298</v>
       </c>
       <c r="D8" t="n">
-        <v>385</v>
+        <v>388</v>
       </c>
     </row>
     <row r="9">
@@ -6168,10 +6168,10 @@
         <v>47</v>
       </c>
       <c r="C9" t="n">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D9" t="n">
-        <v>278</v>
+        <v>281</v>
       </c>
     </row>
     <row r="10">
@@ -6179,7 +6179,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C10" t="n">
         <v>174</v>
@@ -6210,7 +6210,7 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D12" t="n">
         <v>152</v>
@@ -6224,7 +6224,7 @@
         <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D13" t="n">
         <v>120</v>
@@ -6235,7 +6235,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
         <v>64</v>
@@ -6252,7 +6252,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D15" t="n">
         <v>79</v>
@@ -6322,7 +6322,7 @@
         <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -6339,7 +6339,7 @@
         <v>83</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4771</v>
+        <v>5291</v>
       </c>
       <c r="C2" t="n">
-        <v>7774</v>
+        <v>4515</v>
       </c>
       <c r="D2" t="n">
-        <v>21755</v>
+        <v>26143</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4216</v>
+        <v>3780</v>
       </c>
       <c r="C3" t="n">
-        <v>5640</v>
+        <v>6817</v>
       </c>
       <c r="D3" t="n">
-        <v>12860</v>
+        <v>13788</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2863</v>
+        <v>2551</v>
       </c>
       <c r="C4" t="n">
-        <v>4837</v>
+        <v>5899</v>
       </c>
       <c r="D4" t="n">
-        <v>5848</v>
+        <v>5927</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1549</v>
+        <v>1502</v>
       </c>
       <c r="C5" t="n">
-        <v>3288</v>
+        <v>3104</v>
       </c>
       <c r="D5" t="n">
-        <v>2147</v>
+        <v>2013</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>741</v>
+        <v>805</v>
       </c>
       <c r="C6" t="n">
-        <v>2418</v>
+        <v>2295</v>
       </c>
       <c r="D6" t="n">
-        <v>999</v>
+        <v>940</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>298</v>
+        <v>322</v>
       </c>
       <c r="C7" t="n">
-        <v>1416</v>
+        <v>1336</v>
       </c>
       <c r="D7" t="n">
-        <v>601</v>
+        <v>591</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="C8" t="n">
-        <v>605</v>
+        <v>547</v>
       </c>
       <c r="D8" t="n">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C9" t="n">
-        <v>264</v>
+        <v>250</v>
       </c>
       <c r="D9" t="n">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="10">
@@ -6490,10 +6490,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C10" t="n">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="D10" t="n">
         <v>241</v>
@@ -6521,7 +6521,7 @@
         <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D12" t="n">
         <v>155</v>
@@ -6549,7 +6549,7 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D14" t="n">
         <v>100</v>
@@ -6563,7 +6563,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D15" t="n">
         <v>79</v>
@@ -6633,7 +6633,7 @@
         <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -6647,10 +6647,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_population_iteration_40_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_40_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6239</v>
+        <v>1278</v>
       </c>
       <c r="C2" t="n">
-        <v>11524</v>
+        <v>1707</v>
       </c>
       <c r="D2" t="n">
-        <v>24275</v>
+        <v>10906</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3718</v>
+        <v>1977</v>
       </c>
       <c r="C3" t="n">
-        <v>4931</v>
+        <v>4498</v>
       </c>
       <c r="D3" t="n">
-        <v>14827</v>
+        <v>10838</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2666</v>
+        <v>1175</v>
       </c>
       <c r="C4" t="n">
-        <v>6261</v>
+        <v>7074</v>
       </c>
       <c r="D4" t="n">
-        <v>7048</v>
+        <v>5627</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1747</v>
+        <v>590</v>
       </c>
       <c r="C5" t="n">
-        <v>4461</v>
+        <v>4685</v>
       </c>
       <c r="D5" t="n">
-        <v>2628</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1035</v>
+        <v>251</v>
       </c>
       <c r="C6" t="n">
-        <v>2644</v>
+        <v>1862</v>
       </c>
       <c r="D6" t="n">
-        <v>1093</v>
+        <v>740</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>483</v>
+        <v>101</v>
       </c>
       <c r="C7" t="n">
-        <v>1805</v>
+        <v>731</v>
       </c>
       <c r="D7" t="n">
-        <v>643</v>
+        <v>493</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>179</v>
+        <v>74</v>
       </c>
       <c r="C8" t="n">
-        <v>917</v>
+        <v>353</v>
       </c>
       <c r="D8" t="n">
-        <v>432</v>
+        <v>371</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>67</v>
+        <v>54</v>
       </c>
       <c r="C9" t="n">
-        <v>381</v>
+        <v>289</v>
       </c>
       <c r="D9" t="n">
-        <v>310</v>
+        <v>316</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="C10" t="n">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="D10" t="n">
-        <v>244</v>
+        <v>270</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>177</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>212</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>129</v>
+        <v>112</v>
       </c>
       <c r="D12" t="n">
-        <v>160</v>
+        <v>174</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>98</v>
+        <v>77</v>
       </c>
       <c r="D13" t="n">
-        <v>124</v>
+        <v>138</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>89</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>39</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>142</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6730</v>
+        <v>1478</v>
       </c>
       <c r="C2" t="n">
-        <v>11326</v>
+        <v>3684</v>
       </c>
       <c r="D2" t="n">
-        <v>29259</v>
+        <v>20808</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3933</v>
+        <v>1393</v>
       </c>
       <c r="C3" t="n">
-        <v>6976</v>
+        <v>2619</v>
       </c>
       <c r="D3" t="n">
-        <v>15115</v>
+        <v>10068</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2693</v>
+        <v>1352</v>
       </c>
       <c r="C4" t="n">
-        <v>5432</v>
+        <v>5492</v>
       </c>
       <c r="D4" t="n">
-        <v>8103</v>
+        <v>6456</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1893</v>
+        <v>762</v>
       </c>
       <c r="C5" t="n">
-        <v>5214</v>
+        <v>5916</v>
       </c>
       <c r="D5" t="n">
-        <v>3201</v>
+        <v>2614</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1222</v>
+        <v>369</v>
       </c>
       <c r="C6" t="n">
-        <v>3412</v>
+        <v>3296</v>
       </c>
       <c r="D6" t="n">
-        <v>1314</v>
+        <v>957</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>649</v>
+        <v>148</v>
       </c>
       <c r="C7" t="n">
-        <v>2182</v>
+        <v>1292</v>
       </c>
       <c r="D7" t="n">
-        <v>696</v>
+        <v>526</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>268</v>
+        <v>79</v>
       </c>
       <c r="C8" t="n">
-        <v>1290</v>
+        <v>530</v>
       </c>
       <c r="D8" t="n">
-        <v>458</v>
+        <v>385</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>98</v>
+        <v>57</v>
       </c>
       <c r="C9" t="n">
-        <v>606</v>
+        <v>322</v>
       </c>
       <c r="D9" t="n">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="C10" t="n">
-        <v>280</v>
+        <v>246</v>
       </c>
       <c r="D10" t="n">
-        <v>250</v>
+        <v>275</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="C11" t="n">
-        <v>185</v>
+        <v>194</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>217</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="D12" t="n">
-        <v>164</v>
+        <v>176</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>109</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>125</v>
+        <v>141</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C14" t="n">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>102</v>
+        <v>93</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>52</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>95</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>79</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8168</v>
+        <v>769</v>
       </c>
       <c r="C2" t="n">
-        <v>8827</v>
+        <v>1494</v>
       </c>
       <c r="D2" t="n">
-        <v>29224</v>
+        <v>14048</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4123</v>
+        <v>1363</v>
       </c>
       <c r="C3" t="n">
-        <v>7851</v>
+        <v>2931</v>
       </c>
       <c r="D3" t="n">
-        <v>16078</v>
+        <v>11168</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2718</v>
+        <v>1487</v>
       </c>
       <c r="C4" t="n">
-        <v>5933</v>
+        <v>4799</v>
       </c>
       <c r="D4" t="n">
-        <v>8788</v>
+        <v>6985</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1985</v>
+        <v>775</v>
       </c>
       <c r="C5" t="n">
-        <v>5147</v>
+        <v>6470</v>
       </c>
       <c r="D5" t="n">
-        <v>3778</v>
+        <v>2965</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1357</v>
+        <v>305</v>
       </c>
       <c r="C6" t="n">
-        <v>4125</v>
+        <v>4297</v>
       </c>
       <c r="D6" t="n">
-        <v>1568</v>
+        <v>972</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>785</v>
+        <v>74</v>
       </c>
       <c r="C7" t="n">
-        <v>2653</v>
+        <v>1264</v>
       </c>
       <c r="D7" t="n">
-        <v>766</v>
+        <v>555</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>366</v>
+        <v>52</v>
       </c>
       <c r="C8" t="n">
-        <v>1626</v>
+        <v>507</v>
       </c>
       <c r="D8" t="n">
-        <v>485</v>
+        <v>434</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>141</v>
+        <v>27</v>
       </c>
       <c r="C9" t="n">
-        <v>867</v>
+        <v>241</v>
       </c>
       <c r="D9" t="n">
-        <v>331</v>
+        <v>370</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>56</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>395</v>
+        <v>190</v>
       </c>
       <c r="D10" t="n">
-        <v>256</v>
+        <v>212</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>216</v>
+        <v>131</v>
       </c>
       <c r="D11" t="n">
-        <v>207</v>
+        <v>172</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="C12" t="n">
-        <v>156</v>
+        <v>86</v>
       </c>
       <c r="D12" t="n">
-        <v>167</v>
+        <v>138</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>118</v>
+        <v>68</v>
       </c>
       <c r="D13" t="n">
-        <v>126</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>90</v>
+        <v>62</v>
       </c>
       <c r="D14" t="n">
-        <v>103</v>
+        <v>70</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C17" t="n">
-        <v>42</v>
+        <v>93</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>77</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7456</v>
+        <v>909</v>
       </c>
       <c r="C2" t="n">
-        <v>6002</v>
+        <v>3852</v>
       </c>
       <c r="D2" t="n">
-        <v>24150</v>
+        <v>13355</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4915</v>
+        <v>927</v>
       </c>
       <c r="C3" t="n">
-        <v>11045</v>
+        <v>1903</v>
       </c>
       <c r="D3" t="n">
-        <v>17362</v>
+        <v>10819</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1834</v>
+        <v>1257</v>
       </c>
       <c r="C4" t="n">
-        <v>8187</v>
+        <v>3723</v>
       </c>
       <c r="D4" t="n">
-        <v>8348</v>
+        <v>7535</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1253</v>
+        <v>983</v>
       </c>
       <c r="C5" t="n">
-        <v>4042</v>
+        <v>5593</v>
       </c>
       <c r="D5" t="n">
-        <v>2552</v>
+        <v>3597</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>725</v>
+        <v>456</v>
       </c>
       <c r="C6" t="n">
-        <v>2599</v>
+        <v>5337</v>
       </c>
       <c r="D6" t="n">
-        <v>750</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>338</v>
+        <v>140</v>
       </c>
       <c r="C7" t="n">
-        <v>1593</v>
+        <v>2685</v>
       </c>
       <c r="D7" t="n">
-        <v>475</v>
+        <v>616</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>130</v>
+        <v>56</v>
       </c>
       <c r="C8" t="n">
-        <v>849</v>
+        <v>840</v>
       </c>
       <c r="D8" t="n">
-        <v>324</v>
+        <v>449</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="C9" t="n">
-        <v>387</v>
+        <v>347</v>
       </c>
       <c r="D9" t="n">
-        <v>250</v>
+        <v>376</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="C10" t="n">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="D10" t="n">
-        <v>202</v>
+        <v>227</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
         <v>152</v>
       </c>
       <c r="D11" t="n">
-        <v>163</v>
+        <v>177</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>115</v>
+        <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>123</v>
+        <v>143</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>77</v>
+        <v>69</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="D15" t="n">
-        <v>63</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>41</v>
+        <v>90</v>
       </c>
       <c r="D16" t="n">
-        <v>50</v>
+        <v>31</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33</v>
+        <v>103</v>
       </c>
       <c r="D17" t="n">
-        <v>38</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="D18" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4623</v>
+        <v>521</v>
       </c>
       <c r="C2" t="n">
-        <v>2966</v>
+        <v>2037</v>
       </c>
       <c r="D2" t="n">
-        <v>16912</v>
+        <v>9232</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5149</v>
+        <v>803</v>
       </c>
       <c r="C3" t="n">
-        <v>7962</v>
+        <v>2546</v>
       </c>
       <c r="D3" t="n">
-        <v>17285</v>
+        <v>10647</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2595</v>
+        <v>1052</v>
       </c>
       <c r="C4" t="n">
-        <v>9569</v>
+        <v>2879</v>
       </c>
       <c r="D4" t="n">
-        <v>9639</v>
+        <v>7882</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1397</v>
+        <v>1046</v>
       </c>
       <c r="C5" t="n">
-        <v>5862</v>
+        <v>4883</v>
       </c>
       <c r="D5" t="n">
-        <v>3246</v>
+        <v>4085</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>854</v>
+        <v>572</v>
       </c>
       <c r="C6" t="n">
-        <v>3230</v>
+        <v>5650</v>
       </c>
       <c r="D6" t="n">
-        <v>935</v>
+        <v>1520</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>318</v>
+        <v>162</v>
       </c>
       <c r="C7" t="n">
-        <v>2008</v>
+        <v>3726</v>
       </c>
       <c r="D7" t="n">
-        <v>517</v>
+        <v>689</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>108</v>
+        <v>53</v>
       </c>
       <c r="C8" t="n">
-        <v>1099</v>
+        <v>1311</v>
       </c>
       <c r="D8" t="n">
-        <v>338</v>
+        <v>479</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="C9" t="n">
-        <v>435</v>
+        <v>464</v>
       </c>
       <c r="D9" t="n">
-        <v>259</v>
+        <v>378</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C10" t="n">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="D10" t="n">
-        <v>211</v>
+        <v>233</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="D11" t="n">
-        <v>167</v>
+        <v>186</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="D12" t="n">
-        <v>131</v>
+        <v>136</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D13" t="n">
-        <v>97</v>
+        <v>93</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="D14" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>40</v>
+        <v>88</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>32</v>
+        <v>100</v>
       </c>
       <c r="D16" t="n">
-        <v>37</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="D17" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>107</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5653</v>
+        <v>1054</v>
       </c>
       <c r="C2" t="n">
-        <v>10507</v>
+        <v>13668</v>
       </c>
       <c r="D2" t="n">
-        <v>17560</v>
+        <v>10748</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4178</v>
+        <v>573</v>
       </c>
       <c r="C3" t="n">
-        <v>4979</v>
+        <v>2036</v>
       </c>
       <c r="D3" t="n">
-        <v>16072</v>
+        <v>9710</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3147</v>
+        <v>831</v>
       </c>
       <c r="C4" t="n">
-        <v>8583</v>
+        <v>2652</v>
       </c>
       <c r="D4" t="n">
-        <v>10593</v>
+        <v>8120</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1688</v>
+        <v>967</v>
       </c>
       <c r="C5" t="n">
-        <v>7483</v>
+        <v>3819</v>
       </c>
       <c r="D5" t="n">
-        <v>4129</v>
+        <v>4580</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1001</v>
+        <v>706</v>
       </c>
       <c r="C6" t="n">
-        <v>4417</v>
+        <v>5295</v>
       </c>
       <c r="D6" t="n">
-        <v>1255</v>
+        <v>1893</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>461</v>
+        <v>282</v>
       </c>
       <c r="C7" t="n">
-        <v>2553</v>
+        <v>4572</v>
       </c>
       <c r="D7" t="n">
-        <v>569</v>
+        <v>804</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>161</v>
+        <v>82</v>
       </c>
       <c r="C8" t="n">
-        <v>1474</v>
+        <v>2341</v>
       </c>
       <c r="D8" t="n">
-        <v>357</v>
+        <v>502</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>54</v>
+        <v>31</v>
       </c>
       <c r="C9" t="n">
-        <v>686</v>
+        <v>800</v>
       </c>
       <c r="D9" t="n">
-        <v>265</v>
+        <v>390</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C10" t="n">
-        <v>304</v>
+        <v>321</v>
       </c>
       <c r="D10" t="n">
-        <v>216</v>
+        <v>246</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C11" t="n">
+        <v>185</v>
+      </c>
+      <c r="D11" t="n">
         <v>190</v>
-      </c>
-      <c r="D11" t="n">
-        <v>170</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="D12" t="n">
-        <v>133</v>
+        <v>139</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="D14" t="n">
-        <v>63</v>
+        <v>58</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>89</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>35</v>
+        <v>104</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3327</v>
+        <v>691</v>
       </c>
       <c r="C2" t="n">
-        <v>4912</v>
+        <v>6889</v>
       </c>
       <c r="D2" t="n">
-        <v>12259</v>
+        <v>7739</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4408</v>
+        <v>859</v>
       </c>
       <c r="C3" t="n">
-        <v>6685</v>
+        <v>5628</v>
       </c>
       <c r="D3" t="n">
-        <v>15866</v>
+        <v>10400</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3455</v>
+        <v>1301</v>
       </c>
       <c r="C4" t="n">
-        <v>8052</v>
+        <v>3833</v>
       </c>
       <c r="D4" t="n">
-        <v>11292</v>
+        <v>8543</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1765</v>
+        <v>732</v>
       </c>
       <c r="C5" t="n">
-        <v>8896</v>
+        <v>6537</v>
       </c>
       <c r="D5" t="n">
-        <v>4364</v>
+        <v>4319</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>832</v>
+        <v>260</v>
       </c>
       <c r="C6" t="n">
-        <v>5253</v>
+        <v>5881</v>
       </c>
       <c r="D6" t="n">
-        <v>1234</v>
+        <v>1634</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>148</v>
+        <v>75</v>
       </c>
       <c r="C7" t="n">
-        <v>2673</v>
+        <v>2294</v>
       </c>
       <c r="D7" t="n">
-        <v>572</v>
+        <v>610</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="C8" t="n">
-        <v>1120</v>
+        <v>784</v>
       </c>
       <c r="D8" t="n">
-        <v>377</v>
+        <v>382</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C9" t="n">
-        <v>297</v>
+        <v>314</v>
       </c>
       <c r="D9" t="n">
-        <v>289</v>
+        <v>241</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
+        <v>181</v>
+      </c>
+      <c r="D10" t="n">
         <v>186</v>
-      </c>
-      <c r="D10" t="n">
-        <v>166</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="D11" t="n">
-        <v>130</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>43</v>
+        <v>87</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>34</v>
+        <v>101</v>
       </c>
       <c r="D15" t="n">
-        <v>35</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3551</v>
+        <v>356</v>
       </c>
       <c r="C2" t="n">
-        <v>8535</v>
+        <v>2741</v>
       </c>
       <c r="D2" t="n">
-        <v>12466</v>
+        <v>6220</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3382</v>
+        <v>660</v>
       </c>
       <c r="C3" t="n">
-        <v>5237</v>
+        <v>5505</v>
       </c>
       <c r="D3" t="n">
-        <v>14461</v>
+        <v>9234</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3378</v>
+        <v>913</v>
       </c>
       <c r="C4" t="n">
-        <v>7318</v>
+        <v>4549</v>
       </c>
       <c r="D4" t="n">
-        <v>11651</v>
+        <v>8270</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2155</v>
+        <v>697</v>
       </c>
       <c r="C5" t="n">
-        <v>8423</v>
+        <v>4589</v>
       </c>
       <c r="D5" t="n">
-        <v>5228</v>
+        <v>4474</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1066</v>
+        <v>263</v>
       </c>
       <c r="C6" t="n">
-        <v>6761</v>
+        <v>5162</v>
       </c>
       <c r="D6" t="n">
-        <v>1638</v>
+        <v>1720</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>315</v>
+        <v>65</v>
       </c>
       <c r="C7" t="n">
-        <v>3709</v>
+        <v>2846</v>
       </c>
       <c r="D7" t="n">
-        <v>656</v>
+        <v>600</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>67</v>
+        <v>14</v>
       </c>
       <c r="C8" t="n">
-        <v>1715</v>
+        <v>920</v>
       </c>
       <c r="D8" t="n">
-        <v>397</v>
+        <v>331</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="C9" t="n">
-        <v>560</v>
+        <v>299</v>
       </c>
       <c r="D9" t="n">
-        <v>296</v>
+        <v>193</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>223</v>
+        <v>137</v>
       </c>
       <c r="D10" t="n">
-        <v>175</v>
+        <v>142</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>135</v>
+        <v>79</v>
       </c>
       <c r="D11" t="n">
-        <v>134</v>
+        <v>100</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>82</v>
+        <v>54</v>
       </c>
       <c r="D12" t="n">
-        <v>99</v>
+        <v>63</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2463</v>
+        <v>496</v>
       </c>
       <c r="C2" t="n">
-        <v>4711</v>
+        <v>4029</v>
       </c>
       <c r="D2" t="n">
-        <v>9278</v>
+        <v>8882</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3011</v>
+        <v>429</v>
       </c>
       <c r="C3" t="n">
-        <v>5920</v>
+        <v>3451</v>
       </c>
       <c r="D3" t="n">
-        <v>13573</v>
+        <v>8136</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3109</v>
+        <v>687</v>
       </c>
       <c r="C4" t="n">
-        <v>6537</v>
+        <v>5005</v>
       </c>
       <c r="D4" t="n">
-        <v>11759</v>
+        <v>8203</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2385</v>
+        <v>726</v>
       </c>
       <c r="C5" t="n">
-        <v>8178</v>
+        <v>4515</v>
       </c>
       <c r="D5" t="n">
-        <v>5797</v>
+        <v>5030</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1247</v>
+        <v>426</v>
       </c>
       <c r="C6" t="n">
-        <v>7542</v>
+        <v>4800</v>
       </c>
       <c r="D6" t="n">
-        <v>1976</v>
+        <v>2172</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>284</v>
+        <v>136</v>
       </c>
       <c r="C7" t="n">
-        <v>4679</v>
+        <v>4075</v>
       </c>
       <c r="D7" t="n">
-        <v>728</v>
+        <v>780</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>55</v>
+        <v>31</v>
       </c>
       <c r="C8" t="n">
-        <v>2186</v>
+        <v>1872</v>
       </c>
       <c r="D8" t="n">
-        <v>409</v>
+        <v>369</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C9" t="n">
-        <v>636</v>
+        <v>587</v>
       </c>
       <c r="D9" t="n">
-        <v>294</v>
+        <v>211</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>229</v>
+        <v>209</v>
       </c>
       <c r="D10" t="n">
-        <v>178</v>
+        <v>148</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>132</v>
+        <v>103</v>
       </c>
       <c r="D11" t="n">
-        <v>135</v>
+        <v>103</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>79</v>
+        <v>63</v>
       </c>
       <c r="D12" t="n">
-        <v>92</v>
+        <v>66</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="D14" t="n">
-        <v>36</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>56</v>
+        <v>12</v>
       </c>
       <c r="D15" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3484,7 +3484,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3227</v>
+        <v>582</v>
       </c>
       <c r="C2" t="n">
-        <v>10646</v>
+        <v>4838</v>
       </c>
       <c r="D2" t="n">
-        <v>15780</v>
+        <v>14324</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2376</v>
+        <v>379</v>
       </c>
       <c r="C3" t="n">
-        <v>4897</v>
+        <v>3262</v>
       </c>
       <c r="D3" t="n">
-        <v>12188</v>
+        <v>7676</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2672</v>
+        <v>495</v>
       </c>
       <c r="C4" t="n">
-        <v>6083</v>
+        <v>4065</v>
       </c>
       <c r="D4" t="n">
-        <v>11662</v>
+        <v>7941</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2394</v>
+        <v>639</v>
       </c>
       <c r="C5" t="n">
-        <v>7346</v>
+        <v>4675</v>
       </c>
       <c r="D5" t="n">
-        <v>6422</v>
+        <v>5425</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1512</v>
+        <v>520</v>
       </c>
       <c r="C6" t="n">
-        <v>7796</v>
+        <v>4605</v>
       </c>
       <c r="D6" t="n">
-        <v>2427</v>
+        <v>2587</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>519</v>
+        <v>238</v>
       </c>
       <c r="C7" t="n">
-        <v>5715</v>
+        <v>4428</v>
       </c>
       <c r="D7" t="n">
-        <v>867</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>105</v>
+        <v>67</v>
       </c>
       <c r="C8" t="n">
-        <v>3040</v>
+        <v>2907</v>
       </c>
       <c r="D8" t="n">
-        <v>439</v>
+        <v>429</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="C9" t="n">
-        <v>1143</v>
+        <v>1166</v>
       </c>
       <c r="D9" t="n">
-        <v>302</v>
+        <v>230</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>350</v>
+        <v>371</v>
       </c>
       <c r="D10" t="n">
-        <v>186</v>
+        <v>155</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>160</v>
+        <v>146</v>
       </c>
       <c r="D11" t="n">
-        <v>138</v>
+        <v>108</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="D12" t="n">
-        <v>94</v>
+        <v>70</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D13" t="n">
-        <v>64</v>
+        <v>38</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="D14" t="n">
-        <v>37</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>59</v>
+        <v>26</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>67</v>
+        <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4858</v>
+        <v>3212</v>
       </c>
       <c r="C2" t="n">
-        <v>7138</v>
+        <v>10918</v>
       </c>
       <c r="D2" t="n">
-        <v>7721</v>
+        <v>10816</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>843</v>
+        <v>855</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>175</v>
+        <v>205</v>
       </c>
       <c r="C4" t="n">
-        <v>313</v>
+        <v>344</v>
       </c>
       <c r="D4" t="n">
-        <v>1805</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>249</v>
+        <v>314</v>
       </c>
       <c r="C5" t="n">
-        <v>515</v>
+        <v>586</v>
       </c>
       <c r="D5" t="n">
-        <v>1038</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>182</v>
+        <v>255</v>
       </c>
       <c r="C6" t="n">
-        <v>395</v>
+        <v>488</v>
       </c>
       <c r="D6" t="n">
-        <v>777</v>
+        <v>898</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>129</v>
+        <v>202</v>
       </c>
       <c r="C7" t="n">
-        <v>293</v>
+        <v>388</v>
       </c>
       <c r="D7" t="n">
-        <v>496</v>
+        <v>596</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>99</v>
+        <v>171</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>420</v>
+        <v>531</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>75</v>
+        <v>136</v>
       </c>
       <c r="C9" t="n">
-        <v>187</v>
+        <v>277</v>
       </c>
       <c r="D9" t="n">
-        <v>349</v>
+        <v>445</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>53</v>
+        <v>105</v>
       </c>
       <c r="C10" t="n">
-        <v>173</v>
+        <v>265</v>
       </c>
       <c r="D10" t="n">
-        <v>362</v>
+        <v>485</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="C11" t="n">
-        <v>137</v>
+        <v>215</v>
       </c>
       <c r="D11" t="n">
-        <v>245</v>
+        <v>327</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="C12" t="n">
-        <v>104</v>
+        <v>169</v>
       </c>
       <c r="D12" t="n">
-        <v>196</v>
+        <v>274</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="C13" t="n">
-        <v>84</v>
+        <v>142</v>
       </c>
       <c r="D13" t="n">
-        <v>168</v>
+        <v>234</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>128</v>
       </c>
       <c r="D14" t="n">
-        <v>145</v>
+        <v>207</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C15" t="n">
-        <v>72</v>
+        <v>127</v>
       </c>
       <c r="D15" t="n">
-        <v>117</v>
+        <v>171</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>124</v>
       </c>
       <c r="D16" t="n">
-        <v>97</v>
+        <v>140</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="C17" t="n">
-        <v>66</v>
+        <v>119</v>
       </c>
       <c r="D17" t="n">
-        <v>76</v>
+        <v>114</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C18" t="n">
-        <v>63</v>
+        <v>116</v>
       </c>
       <c r="D18" t="n">
-        <v>57</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C19" t="n">
-        <v>60</v>
+        <v>111</v>
       </c>
       <c r="D19" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>109</v>
       </c>
       <c r="D20" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21">
@@ -4156,10 +4156,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C21" t="n">
-        <v>72</v>
+        <v>131</v>
       </c>
       <c r="D21" t="n">
         <v>1</v>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2335</v>
+        <v>519</v>
       </c>
       <c r="C2" t="n">
-        <v>6132</v>
+        <v>7870</v>
       </c>
       <c r="D2" t="n">
-        <v>11740</v>
+        <v>14461</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3147</v>
+        <v>382</v>
       </c>
       <c r="C3" t="n">
-        <v>6615</v>
+        <v>3508</v>
       </c>
       <c r="D3" t="n">
-        <v>13367</v>
+        <v>8064</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3579</v>
+        <v>384</v>
       </c>
       <c r="C4" t="n">
-        <v>8637</v>
+        <v>3587</v>
       </c>
       <c r="D4" t="n">
-        <v>11953</v>
+        <v>7580</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1441</v>
+        <v>533</v>
       </c>
       <c r="C5" t="n">
-        <v>10913</v>
+        <v>4290</v>
       </c>
       <c r="D5" t="n">
-        <v>5813</v>
+        <v>5670</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>479</v>
+        <v>528</v>
       </c>
       <c r="C6" t="n">
-        <v>7052</v>
+        <v>4546</v>
       </c>
       <c r="D6" t="n">
-        <v>1928</v>
+        <v>2988</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>97</v>
+        <v>323</v>
       </c>
       <c r="C7" t="n">
-        <v>2979</v>
+        <v>4506</v>
       </c>
       <c r="D7" t="n">
-        <v>540</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>20</v>
+        <v>120</v>
       </c>
       <c r="C8" t="n">
-        <v>1120</v>
+        <v>3561</v>
       </c>
       <c r="D8" t="n">
-        <v>295</v>
+        <v>509</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="C9" t="n">
-        <v>343</v>
+        <v>1870</v>
       </c>
       <c r="D9" t="n">
-        <v>182</v>
+        <v>252</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C10" t="n">
-        <v>156</v>
+        <v>690</v>
       </c>
       <c r="D10" t="n">
-        <v>135</v>
+        <v>163</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>90</v>
+        <v>231</v>
       </c>
       <c r="D11" t="n">
-        <v>92</v>
+        <v>112</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>50</v>
+        <v>103</v>
       </c>
       <c r="D12" t="n">
-        <v>62</v>
+        <v>73</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>37</v>
+        <v>64</v>
       </c>
       <c r="D13" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D14" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>65</v>
+        <v>35</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7082</v>
+        <v>4367</v>
       </c>
       <c r="C2" t="n">
-        <v>7387</v>
+        <v>6384</v>
       </c>
       <c r="D2" t="n">
-        <v>11380</v>
+        <v>23932</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2065</v>
+        <v>1063</v>
       </c>
       <c r="C3" t="n">
-        <v>3597</v>
+        <v>4311</v>
       </c>
       <c r="D3" t="n">
-        <v>1936</v>
+        <v>2093</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C4" t="n">
-        <v>114</v>
+        <v>134</v>
       </c>
       <c r="D4" t="n">
-        <v>1538</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>191</v>
+        <v>148</v>
       </c>
       <c r="C5" t="n">
-        <v>384</v>
+        <v>334</v>
       </c>
       <c r="D5" t="n">
-        <v>1161</v>
+        <v>986</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>202</v>
+        <v>143</v>
       </c>
       <c r="C6" t="n">
-        <v>459</v>
+        <v>360</v>
       </c>
       <c r="D6" t="n">
-        <v>808</v>
+        <v>712</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>102</v>
       </c>
       <c r="C7" t="n">
-        <v>350</v>
+        <v>277</v>
       </c>
       <c r="D7" t="n">
-        <v>546</v>
+        <v>466</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="C8" t="n">
-        <v>260</v>
+        <v>206</v>
       </c>
       <c r="D8" t="n">
-        <v>429</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="C9" t="n">
-        <v>205</v>
+        <v>169</v>
       </c>
       <c r="D9" t="n">
-        <v>354</v>
+        <v>313</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="C10" t="n">
-        <v>180</v>
+        <v>153</v>
       </c>
       <c r="D10" t="n">
-        <v>356</v>
+        <v>324</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>154</v>
+        <v>128</v>
       </c>
       <c r="D11" t="n">
-        <v>261</v>
+        <v>231</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C12" t="n">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>199</v>
+        <v>182</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>154</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>133</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>118</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="D18" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>10</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C21" t="n">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5665</v>
+        <v>2475</v>
       </c>
       <c r="C2" t="n">
-        <v>4784</v>
+        <v>6254</v>
       </c>
       <c r="D2" t="n">
-        <v>20683</v>
+        <v>19423</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3751</v>
+        <v>2303</v>
       </c>
       <c r="C3" t="n">
-        <v>5010</v>
+        <v>4768</v>
       </c>
       <c r="D3" t="n">
-        <v>3380</v>
+        <v>5779</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>930</v>
+        <v>518</v>
       </c>
       <c r="C4" t="n">
-        <v>2150</v>
+        <v>2737</v>
       </c>
       <c r="D4" t="n">
-        <v>1571</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="C5" t="n">
-        <v>220</v>
+        <v>206</v>
       </c>
       <c r="D5" t="n">
-        <v>1186</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>185</v>
+        <v>137</v>
       </c>
       <c r="C6" t="n">
-        <v>411</v>
+        <v>343</v>
       </c>
       <c r="D6" t="n">
-        <v>864</v>
+        <v>747</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>159</v>
+        <v>113</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>324</v>
       </c>
       <c r="D7" t="n">
-        <v>589</v>
+        <v>509</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>115</v>
+        <v>83</v>
       </c>
       <c r="C8" t="n">
-        <v>307</v>
+        <v>244</v>
       </c>
       <c r="D8" t="n">
-        <v>441</v>
+        <v>395</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="C9" t="n">
-        <v>230</v>
+        <v>188</v>
       </c>
       <c r="D9" t="n">
-        <v>363</v>
+        <v>319</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="C10" t="n">
-        <v>192</v>
+        <v>161</v>
       </c>
       <c r="D10" t="n">
-        <v>352</v>
+        <v>318</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>140</v>
       </c>
       <c r="D11" t="n">
-        <v>270</v>
+        <v>244</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C12" t="n">
-        <v>135</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>206</v>
+        <v>187</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>172</v>
+        <v>155</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>9</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C21" t="n">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5077</v>
+        <v>2177</v>
       </c>
       <c r="C2" t="n">
-        <v>4207</v>
+        <v>6332</v>
       </c>
       <c r="D2" t="n">
-        <v>27693</v>
+        <v>19805</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3850</v>
+        <v>1971</v>
       </c>
       <c r="C3" t="n">
-        <v>4229</v>
+        <v>4841</v>
       </c>
       <c r="D3" t="n">
-        <v>5905</v>
+        <v>7645</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1977</v>
+        <v>1240</v>
       </c>
       <c r="C4" t="n">
-        <v>3725</v>
+        <v>3888</v>
       </c>
       <c r="D4" t="n">
-        <v>1870</v>
+        <v>2346</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>442</v>
+        <v>268</v>
       </c>
       <c r="C5" t="n">
-        <v>1271</v>
+        <v>1659</v>
       </c>
       <c r="D5" t="n">
-        <v>1208</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>147</v>
+        <v>111</v>
       </c>
       <c r="C6" t="n">
-        <v>301</v>
+        <v>262</v>
       </c>
       <c r="D6" t="n">
-        <v>910</v>
+        <v>794</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>116</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>334</v>
       </c>
       <c r="D7" t="n">
-        <v>625</v>
+        <v>548</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>125</v>
+        <v>90</v>
       </c>
       <c r="C8" t="n">
-        <v>358</v>
+        <v>286</v>
       </c>
       <c r="D8" t="n">
-        <v>462</v>
+        <v>407</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>90</v>
+        <v>67</v>
       </c>
       <c r="C9" t="n">
-        <v>267</v>
+        <v>216</v>
       </c>
       <c r="D9" t="n">
-        <v>372</v>
+        <v>329</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="C10" t="n">
-        <v>207</v>
+        <v>174</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>314</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="C11" t="n">
-        <v>177</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>280</v>
+        <v>250</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C12" t="n">
-        <v>148</v>
+        <v>125</v>
       </c>
       <c r="D12" t="n">
-        <v>211</v>
+        <v>194</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C13" t="n">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>175</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C15" t="n">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C21" t="n">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4811</v>
+        <v>1608</v>
       </c>
       <c r="C2" t="n">
-        <v>5979</v>
+        <v>7583</v>
       </c>
       <c r="D2" t="n">
-        <v>24840</v>
+        <v>15689</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3647</v>
+        <v>1710</v>
       </c>
       <c r="C3" t="n">
-        <v>3671</v>
+        <v>4944</v>
       </c>
       <c r="D3" t="n">
-        <v>8801</v>
+        <v>9040</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2468</v>
+        <v>1389</v>
       </c>
       <c r="C4" t="n">
-        <v>3918</v>
+        <v>4309</v>
       </c>
       <c r="D4" t="n">
-        <v>2549</v>
+        <v>3292</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>986</v>
+        <v>640</v>
       </c>
       <c r="C5" t="n">
-        <v>2504</v>
+        <v>2865</v>
       </c>
       <c r="D5" t="n">
-        <v>1274</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>258</v>
+        <v>170</v>
       </c>
       <c r="C6" t="n">
-        <v>791</v>
+        <v>1009</v>
       </c>
       <c r="D6" t="n">
-        <v>948</v>
+        <v>838</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>144</v>
+        <v>107</v>
       </c>
       <c r="C7" t="n">
-        <v>354</v>
+        <v>295</v>
       </c>
       <c r="D7" t="n">
-        <v>659</v>
+        <v>580</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>131</v>
+        <v>95</v>
       </c>
       <c r="C8" t="n">
-        <v>378</v>
+        <v>310</v>
       </c>
       <c r="D8" t="n">
-        <v>484</v>
+        <v>427</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>96</v>
+        <v>71</v>
       </c>
       <c r="C9" t="n">
-        <v>309</v>
+        <v>250</v>
       </c>
       <c r="D9" t="n">
-        <v>378</v>
+        <v>338</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="C10" t="n">
-        <v>233</v>
+        <v>193</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>310</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="C11" t="n">
-        <v>188</v>
+        <v>160</v>
       </c>
       <c r="D11" t="n">
-        <v>286</v>
+        <v>257</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>160</v>
+        <v>135</v>
       </c>
       <c r="D12" t="n">
-        <v>216</v>
+        <v>200</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C13" t="n">
-        <v>128</v>
+        <v>109</v>
       </c>
       <c r="D13" t="n">
-        <v>178</v>
+        <v>159</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="D15" t="n">
-        <v>122</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C16" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C21" t="n">
-        <v>137</v>
+        <v>120</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6082</v>
+        <v>2019</v>
       </c>
       <c r="C2" t="n">
-        <v>12597</v>
+        <v>4930</v>
       </c>
       <c r="D2" t="n">
-        <v>29339</v>
+        <v>16398</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3068</v>
+        <v>1376</v>
       </c>
       <c r="C3" t="n">
-        <v>3973</v>
+        <v>5546</v>
       </c>
       <c r="D3" t="n">
-        <v>9990</v>
+        <v>9414</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1885</v>
+        <v>1335</v>
       </c>
       <c r="C4" t="n">
-        <v>3068</v>
+        <v>4519</v>
       </c>
       <c r="D4" t="n">
-        <v>3153</v>
+        <v>4208</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>894</v>
+        <v>863</v>
       </c>
       <c r="C5" t="n">
-        <v>2375</v>
+        <v>3567</v>
       </c>
       <c r="D5" t="n">
-        <v>1169</v>
+        <v>1610</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>296</v>
+        <v>351</v>
       </c>
       <c r="C6" t="n">
-        <v>1114</v>
+        <v>1942</v>
       </c>
       <c r="D6" t="n">
-        <v>763</v>
+        <v>903</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>88</v>
+        <v>124</v>
       </c>
       <c r="C7" t="n">
-        <v>360</v>
+        <v>651</v>
       </c>
       <c r="D7" t="n">
-        <v>513</v>
+        <v>611</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>59</v>
+        <v>94</v>
       </c>
       <c r="C8" t="n">
-        <v>223</v>
+        <v>302</v>
       </c>
       <c r="D8" t="n">
-        <v>364</v>
+        <v>448</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="C9" t="n">
-        <v>197</v>
+        <v>275</v>
       </c>
       <c r="D9" t="n">
-        <v>270</v>
+        <v>348</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="C10" t="n">
-        <v>151</v>
+        <v>218</v>
       </c>
       <c r="D10" t="n">
-        <v>237</v>
+        <v>307</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="C11" t="n">
-        <v>114</v>
+        <v>174</v>
       </c>
       <c r="D11" t="n">
-        <v>194</v>
+        <v>262</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>92</v>
+        <v>145</v>
       </c>
       <c r="D12" t="n">
-        <v>148</v>
+        <v>205</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="C13" t="n">
-        <v>74</v>
+        <v>119</v>
       </c>
       <c r="D13" t="n">
-        <v>117</v>
+        <v>161</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>94</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>137</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>45</v>
+        <v>76</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C16" t="n">
-        <v>38</v>
+        <v>67</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>75</v>
+        <v>133</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5424</v>
+        <v>3093</v>
       </c>
       <c r="C2" t="n">
-        <v>7922</v>
+        <v>5096</v>
       </c>
       <c r="D2" t="n">
-        <v>25484</v>
+        <v>17367</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3807</v>
+        <v>1367</v>
       </c>
       <c r="C3" t="n">
-        <v>7822</v>
+        <v>4592</v>
       </c>
       <c r="D3" t="n">
-        <v>12644</v>
+        <v>9772</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2172</v>
+        <v>1164</v>
       </c>
       <c r="C4" t="n">
-        <v>3560</v>
+        <v>4904</v>
       </c>
       <c r="D4" t="n">
-        <v>4501</v>
+        <v>4979</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1232</v>
+        <v>959</v>
       </c>
       <c r="C5" t="n">
-        <v>2738</v>
+        <v>3968</v>
       </c>
       <c r="D5" t="n">
-        <v>1533</v>
+        <v>1969</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>555</v>
+        <v>521</v>
       </c>
       <c r="C6" t="n">
-        <v>1826</v>
+        <v>2701</v>
       </c>
       <c r="D6" t="n">
-        <v>822</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>175</v>
+        <v>200</v>
       </c>
       <c r="C7" t="n">
-        <v>788</v>
+        <v>1258</v>
       </c>
       <c r="D7" t="n">
-        <v>556</v>
+        <v>644</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>67</v>
+        <v>98</v>
       </c>
       <c r="C8" t="n">
-        <v>298</v>
+        <v>456</v>
       </c>
       <c r="D8" t="n">
-        <v>388</v>
+        <v>468</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>47</v>
+        <v>76</v>
       </c>
       <c r="C9" t="n">
-        <v>210</v>
+        <v>286</v>
       </c>
       <c r="D9" t="n">
-        <v>281</v>
+        <v>355</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="C10" t="n">
-        <v>174</v>
+        <v>241</v>
       </c>
       <c r="D10" t="n">
-        <v>240</v>
+        <v>309</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="C11" t="n">
-        <v>132</v>
+        <v>191</v>
       </c>
       <c r="D11" t="n">
-        <v>199</v>
+        <v>265</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="C12" t="n">
-        <v>101</v>
+        <v>154</v>
       </c>
       <c r="D12" t="n">
-        <v>152</v>
+        <v>208</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>82</v>
+        <v>128</v>
       </c>
       <c r="D13" t="n">
-        <v>120</v>
+        <v>164</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>64</v>
+        <v>102</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>137</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>81</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>69</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>93</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>41</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="C21" t="n">
-        <v>83</v>
+        <v>145</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5291</v>
+        <v>2684</v>
       </c>
       <c r="C2" t="n">
-        <v>4515</v>
+        <v>3098</v>
       </c>
       <c r="D2" t="n">
-        <v>26143</v>
+        <v>13664</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3780</v>
+        <v>1946</v>
       </c>
       <c r="C3" t="n">
-        <v>6817</v>
+        <v>6987</v>
       </c>
       <c r="D3" t="n">
-        <v>13788</v>
+        <v>10996</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2551</v>
+        <v>886</v>
       </c>
       <c r="C4" t="n">
-        <v>5899</v>
+        <v>6916</v>
       </c>
       <c r="D4" t="n">
-        <v>5927</v>
+        <v>4697</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1502</v>
+        <v>481</v>
       </c>
       <c r="C5" t="n">
-        <v>3104</v>
+        <v>2646</v>
       </c>
       <c r="D5" t="n">
-        <v>2013</v>
+        <v>1571</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>805</v>
+        <v>184</v>
       </c>
       <c r="C6" t="n">
-        <v>2295</v>
+        <v>1232</v>
       </c>
       <c r="D6" t="n">
-        <v>940</v>
+        <v>631</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>322</v>
+        <v>90</v>
       </c>
       <c r="C7" t="n">
-        <v>1336</v>
+        <v>446</v>
       </c>
       <c r="D7" t="n">
-        <v>591</v>
+        <v>458</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>105</v>
+        <v>70</v>
       </c>
       <c r="C8" t="n">
-        <v>547</v>
+        <v>280</v>
       </c>
       <c r="D8" t="n">
-        <v>413</v>
+        <v>347</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C9" t="n">
-        <v>250</v>
+        <v>236</v>
       </c>
       <c r="D9" t="n">
-        <v>295</v>
+        <v>302</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C10" t="n">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="D10" t="n">
-        <v>241</v>
+        <v>259</v>
       </c>
     </row>
     <row r="11">
@@ -6504,10 +6504,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D11" t="n">
         <v>203</v>
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="D12" t="n">
-        <v>155</v>
+        <v>160</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="D13" t="n">
-        <v>123</v>
+        <v>134</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C14" t="n">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>111</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C16" t="n">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>74</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18">
@@ -6602,13 +6602,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19">
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>145</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>91</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
